--- a/docs/지역_DB.xlsx
+++ b/docs/지역_DB.xlsx
@@ -1653,7 +1653,11 @@
       <c r="U15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>노량진 회</t>
+        </is>
+      </c>
       <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
@@ -2183,7 +2187,11 @@
       <c r="U22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>마장동 한우</t>
+        </is>
+      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
           <t>서울숲</t>
@@ -2491,7 +2499,11 @@
       <c r="U26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>신당동 떡볶이</t>
+        </is>
+      </c>
       <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr"/>
@@ -9237,7 +9249,11 @@
       <c r="U110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="2" t="inlineStr"/>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>닭갈비</t>
+        </is>
+      </c>
       <c r="W110" s="2" t="inlineStr">
         <is>
           <t>소양호</t>
@@ -10727,7 +10743,11 @@
       <c r="U127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr">
+        <is>
+          <t>명태</t>
+        </is>
+      </c>
       <c r="W127" s="2" t="inlineStr">
         <is>
           <t>명사십리</t>
@@ -11149,7 +11169,11 @@
       <c r="U132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>문어</t>
+        </is>
+      </c>
       <c r="W132" s="2" t="inlineStr">
         <is>
           <t>총석정</t>
@@ -11793,7 +11817,11 @@
       <c r="U140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr">
+        <is>
+          <t>송이</t>
+        </is>
+      </c>
       <c r="W140" s="2" t="inlineStr"/>
       <c r="X140" s="2" t="inlineStr"/>
       <c r="Y140" s="2" t="inlineStr"/>
@@ -27501,7 +27529,11 @@
       <c r="U328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V328" s="2" t="inlineStr"/>
+      <c r="V328" s="2" t="inlineStr">
+        <is>
+          <t>꿀</t>
+        </is>
+      </c>
       <c r="W328" s="2" t="inlineStr"/>
       <c r="X328" s="2" t="inlineStr"/>
       <c r="Y328" s="2" t="inlineStr"/>
@@ -28043,7 +28075,11 @@
       <c r="U335" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
       <c r="W335" s="2" t="inlineStr"/>
       <c r="X335" s="2" t="inlineStr"/>
       <c r="Y335" s="2" t="inlineStr"/>

--- a/docs/지역_DB.xlsx
+++ b/docs/지역_DB.xlsx
@@ -24163,7 +24163,11 @@
       <c r="U287" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V287" s="2" t="inlineStr"/>
+      <c r="V287" s="2" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
       <c r="W287" s="2" t="inlineStr"/>
       <c r="X287" s="2" t="inlineStr"/>
       <c r="Y287" s="2" t="inlineStr"/>

--- a/docs/지역_DB.xlsx
+++ b/docs/지역_DB.xlsx
@@ -16071,7 +16071,7 @@
       </c>
       <c r="V190" s="2" t="inlineStr">
         <is>
-          <t>꼬막</t>
+          <t>유자</t>
         </is>
       </c>
       <c r="W190" s="2" t="inlineStr"/>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="V238" s="2" t="inlineStr">
         <is>
-          <t>유자</t>
+          <t>죽방멸치</t>
         </is>
       </c>
       <c r="W238" s="2" t="inlineStr"/>

--- a/docs/지역_DB.xlsx
+++ b/docs/지역_DB.xlsx
@@ -2663,7 +2663,11 @@
       <c r="U28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>씨앗호떡</t>
+        </is>
+      </c>
       <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="inlineStr"/>

--- a/docs/지역_DB.xlsx
+++ b/docs/지역_DB.xlsx
@@ -7322,11 +7322,15 @@
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>경기 수원, 경기 화성, 경기 안양, 경기 시흥, 경기 군포, 경기 의왕</t>
+          <t>경기 수원, 경기 화성, 경기 안양, 경기 시흥, 경기 군포, 경기 의왕, 인천 옹진</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>영흥대교·선재대교(대부도) → 인천 옹진</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>경기만</t>
@@ -20813,12 +20817,20 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>무연륙 섬</t>
-        </is>
-      </c>
-      <c r="K246" s="2" t="n"/>
+          <t>연륙 섬</t>
+        </is>
+      </c>
+      <c r="K246" s="2" t="inlineStr">
+        <is>
+          <t>경기 안산</t>
+        </is>
+      </c>
       <c r="L246" s="2" t="n"/>
-      <c r="M246" s="2" t="n"/>
+      <c r="M246" s="2" t="inlineStr">
+        <is>
+          <t>영흥대교·선재대교(대부도) → 경기 안산</t>
+        </is>
+      </c>
       <c r="N246" s="2" t="inlineStr">
         <is>
           <t>경기만</t>
@@ -20843,7 +20855,7 @@
         <v>0</v>
       </c>
       <c r="U246" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V246" s="2" t="inlineStr">
         <is>

--- a/docs/지역_DB.xlsx
+++ b/docs/지역_DB.xlsx
@@ -32435,7 +32435,11 @@
       <c r="U387" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V387" s="2" t="inlineStr"/>
+      <c r="V387" s="2" t="inlineStr">
+        <is>
+          <t>길주 모피</t>
+        </is>
+      </c>
       <c r="W387" s="2" t="inlineStr"/>
       <c r="X387" s="2" t="inlineStr"/>
       <c r="Y387" s="2" t="inlineStr">
@@ -33441,7 +33445,7 @@
       </c>
       <c r="V399" s="2" t="inlineStr">
         <is>
-          <t>강계 포도</t>
+          <t>강계 모피</t>
         </is>
       </c>
       <c r="W399" s="2" t="inlineStr"/>

--- a/docs/지역_DB.xlsx
+++ b/docs/지역_DB.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z428"/>
+  <dimension ref="A1:AA428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
     <col width="6" customWidth="1" min="19" max="19"/>
     <col width="8" customWidth="1" min="20" max="20"/>
     <col width="5" customWidth="1" min="21" max="21"/>
-    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="8" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
@@ -567,25 +567,30 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>공항</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>특산물</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>자연경관</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>석유(턴당)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>탄전</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>자체 발전</t>
         </is>
@@ -663,11 +668,14 @@
       <c r="U2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="2" t="inlineStr"/>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W2" s="2" t="inlineStr"/>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -741,11 +749,14 @@
       <c r="U3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="2" t="inlineStr"/>
+      <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W3" s="2" t="inlineStr"/>
       <c r="X3" s="2" t="inlineStr"/>
       <c r="Y3" s="2" t="inlineStr"/>
       <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -819,11 +830,14 @@
       <c r="U4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W4" s="2" t="inlineStr"/>
       <c r="X4" s="2" t="inlineStr"/>
       <c r="Y4" s="2" t="inlineStr"/>
       <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -897,11 +911,14 @@
       <c r="U5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W5" s="2" t="inlineStr"/>
       <c r="X5" s="2" t="inlineStr"/>
       <c r="Y5" s="2" t="inlineStr"/>
       <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -971,11 +988,14 @@
       <c r="U6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W6" s="2" t="inlineStr"/>
       <c r="X6" s="2" t="inlineStr"/>
       <c r="Y6" s="2" t="inlineStr"/>
       <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1045,11 +1065,14 @@
       <c r="U7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W7" s="2" t="inlineStr"/>
       <c r="X7" s="2" t="inlineStr"/>
       <c r="Y7" s="2" t="inlineStr"/>
       <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1119,11 +1142,14 @@
       <c r="U8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W8" s="2" t="inlineStr"/>
       <c r="X8" s="2" t="inlineStr"/>
       <c r="Y8" s="2" t="inlineStr"/>
       <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1193,11 +1219,14 @@
       <c r="U9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W9" s="2" t="inlineStr"/>
       <c r="X9" s="2" t="inlineStr"/>
       <c r="Y9" s="2" t="inlineStr"/>
       <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1267,11 +1296,14 @@
       <c r="U10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W10" s="2" t="inlineStr"/>
       <c r="X10" s="2" t="inlineStr"/>
       <c r="Y10" s="2" t="inlineStr"/>
       <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1345,11 +1377,14 @@
       <c r="U11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W11" s="2" t="inlineStr"/>
       <c r="X11" s="2" t="inlineStr"/>
       <c r="Y11" s="2" t="inlineStr"/>
       <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1419,11 +1454,14 @@
       <c r="U12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W12" s="2" t="inlineStr"/>
       <c r="X12" s="2" t="inlineStr"/>
       <c r="Y12" s="2" t="inlineStr"/>
       <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1493,11 +1531,14 @@
       <c r="U13" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W13" s="2" t="inlineStr"/>
       <c r="X13" s="2" t="inlineStr"/>
       <c r="Y13" s="2" t="inlineStr"/>
       <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1571,15 +1612,18 @@
       <c r="U14" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V14" s="2" t="inlineStr"/>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>여의도한강공원</t>
         </is>
       </c>
-      <c r="X14" s="2" t="inlineStr"/>
       <c r="Y14" s="2" t="inlineStr"/>
       <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1653,15 +1697,18 @@
       <c r="U15" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>노량진 회</t>
         </is>
       </c>
-      <c r="W15" s="2" t="inlineStr"/>
       <c r="X15" s="2" t="inlineStr"/>
       <c r="Y15" s="2" t="inlineStr"/>
       <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1735,11 +1782,14 @@
       <c r="U16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V16" s="2" t="inlineStr"/>
+      <c r="V16" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W16" s="2" t="inlineStr"/>
       <c r="X16" s="2" t="inlineStr"/>
       <c r="Y16" s="2" t="inlineStr"/>
       <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1809,11 +1859,14 @@
       <c r="U17" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="2" t="inlineStr"/>
+      <c r="V17" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W17" s="2" t="inlineStr"/>
       <c r="X17" s="2" t="inlineStr"/>
       <c r="Y17" s="2" t="inlineStr"/>
       <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1887,11 +1940,14 @@
       <c r="U18" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="2" t="inlineStr"/>
+      <c r="V18" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W18" s="2" t="inlineStr"/>
       <c r="X18" s="2" t="inlineStr"/>
       <c r="Y18" s="2" t="inlineStr"/>
       <c r="Z18" s="2" t="inlineStr"/>
+      <c r="AA18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1961,11 +2017,14 @@
       <c r="U19" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V19" s="2" t="inlineStr"/>
+      <c r="V19" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W19" s="2" t="inlineStr"/>
       <c r="X19" s="2" t="inlineStr"/>
       <c r="Y19" s="2" t="inlineStr"/>
       <c r="Z19" s="2" t="inlineStr"/>
+      <c r="AA19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2035,11 +2094,14 @@
       <c r="U20" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="2" t="inlineStr"/>
+      <c r="V20" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W20" s="2" t="inlineStr"/>
       <c r="X20" s="2" t="inlineStr"/>
       <c r="Y20" s="2" t="inlineStr"/>
       <c r="Z20" s="2" t="inlineStr"/>
+      <c r="AA20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2109,11 +2171,14 @@
       <c r="U21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V21" s="2" t="inlineStr"/>
+      <c r="V21" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W21" s="2" t="inlineStr"/>
       <c r="X21" s="2" t="inlineStr"/>
       <c r="Y21" s="2" t="inlineStr"/>
       <c r="Z21" s="2" t="inlineStr"/>
+      <c r="AA21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2187,19 +2252,22 @@
       <c r="U22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V22" s="2" t="inlineStr">
+      <c r="V22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
         <is>
           <t>마장동 한우</t>
         </is>
       </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>서울숲</t>
         </is>
       </c>
-      <c r="X22" s="2" t="inlineStr"/>
       <c r="Y22" s="2" t="inlineStr"/>
       <c r="Z22" s="2" t="inlineStr"/>
+      <c r="AA22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2269,11 +2337,14 @@
       <c r="U23" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W23" s="2" t="inlineStr"/>
       <c r="X23" s="2" t="inlineStr"/>
       <c r="Y23" s="2" t="inlineStr"/>
       <c r="Z23" s="2" t="inlineStr"/>
+      <c r="AA23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2347,11 +2418,14 @@
       <c r="U24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W24" s="2" t="inlineStr"/>
       <c r="X24" s="2" t="inlineStr"/>
       <c r="Y24" s="2" t="inlineStr"/>
       <c r="Z24" s="2" t="inlineStr"/>
+      <c r="AA24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2421,15 +2495,18 @@
       <c r="U25" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="2" t="inlineStr"/>
-      <c r="W25" s="2" t="inlineStr">
+      <c r="V25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="2" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>인왕산 치마바위</t>
         </is>
       </c>
-      <c r="X25" s="2" t="inlineStr"/>
       <c r="Y25" s="2" t="inlineStr"/>
       <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2499,15 +2576,18 @@
       <c r="U26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="V26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t>신당동 떡볶이</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr"/>
       <c r="X26" s="2" t="inlineStr"/>
       <c r="Y26" s="2" t="inlineStr"/>
       <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2585,15 +2665,18 @@
       <c r="U27" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V27" s="2" t="inlineStr"/>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="V27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="2" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
         <is>
           <t>해운대</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr"/>
       <c r="Y27" s="2" t="inlineStr"/>
       <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2663,15 +2746,18 @@
       <c r="U28" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>씨앗호떡</t>
         </is>
       </c>
-      <c r="W28" s="2" t="inlineStr"/>
       <c r="X28" s="2" t="inlineStr"/>
       <c r="Y28" s="2" t="inlineStr"/>
       <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2753,11 +2839,14 @@
       <c r="U29" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W29" s="2" t="inlineStr"/>
       <c r="X29" s="2" t="inlineStr"/>
       <c r="Y29" s="2" t="inlineStr"/>
       <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -2827,11 +2916,14 @@
       <c r="U30" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W30" s="2" t="inlineStr"/>
       <c r="X30" s="2" t="inlineStr"/>
       <c r="Y30" s="2" t="inlineStr"/>
       <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2905,11 +2997,14 @@
       <c r="U31" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W31" s="2" t="inlineStr"/>
       <c r="X31" s="2" t="inlineStr"/>
       <c r="Y31" s="2" t="inlineStr"/>
       <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -2991,15 +3086,18 @@
       <c r="U32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V32" s="2" t="inlineStr"/>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="V32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>오륙도</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr"/>
       <c r="Y32" s="2" t="inlineStr"/>
       <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3069,11 +3167,14 @@
       <c r="U33" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W33" s="2" t="inlineStr"/>
       <c r="X33" s="2" t="inlineStr"/>
       <c r="Y33" s="2" t="inlineStr"/>
       <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3143,11 +3244,14 @@
       <c r="U34" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W34" s="2" t="inlineStr"/>
       <c r="X34" s="2" t="inlineStr"/>
       <c r="Y34" s="2" t="inlineStr"/>
       <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3221,11 +3325,14 @@
       <c r="U35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W35" s="2" t="inlineStr"/>
       <c r="X35" s="2" t="inlineStr"/>
       <c r="Y35" s="2" t="inlineStr"/>
       <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3307,15 +3414,18 @@
       <c r="U36" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="V36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
         <is>
           <t>멸치</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr"/>
       <c r="X36" s="2" t="inlineStr"/>
       <c r="Y36" s="2" t="inlineStr"/>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr">
         <is>
           <t>2 (원자력(고리))</t>
         </is>
@@ -3397,11 +3507,14 @@
       <c r="U37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W37" s="2" t="inlineStr"/>
       <c r="X37" s="2" t="inlineStr"/>
       <c r="Y37" s="2" t="inlineStr"/>
       <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3487,19 +3600,22 @@
       <c r="U38" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V38" s="2" t="inlineStr">
+      <c r="V38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>토마토</t>
         </is>
       </c>
-      <c r="W38" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>을숙도</t>
         </is>
       </c>
-      <c r="X38" s="2" t="inlineStr"/>
       <c r="Y38" s="2" t="inlineStr"/>
       <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3581,15 +3697,18 @@
       <c r="U39" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="V39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
         <is>
           <t>고등어</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr"/>
       <c r="X39" s="2" t="inlineStr"/>
       <c r="Y39" s="2" t="inlineStr"/>
       <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3675,15 +3794,18 @@
       <c r="U40" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V40" s="2" t="inlineStr"/>
-      <c r="W40" s="2" t="inlineStr">
+      <c r="V40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>태종대</t>
         </is>
       </c>
-      <c r="X40" s="2" t="inlineStr"/>
       <c r="Y40" s="2" t="inlineStr"/>
       <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3761,11 +3883,14 @@
       <c r="U41" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W41" s="2" t="inlineStr"/>
       <c r="X41" s="2" t="inlineStr"/>
       <c r="Y41" s="2" t="inlineStr"/>
       <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3845,13 +3970,16 @@
         <v>0</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V42" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W42" s="2" t="inlineStr"/>
       <c r="X42" s="2" t="inlineStr"/>
       <c r="Y42" s="2" t="inlineStr"/>
       <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3925,15 +4053,18 @@
       <c r="U43" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="2" t="inlineStr">
+      <c r="V43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>막창</t>
         </is>
       </c>
-      <c r="W43" s="2" t="inlineStr"/>
       <c r="X43" s="2" t="inlineStr"/>
       <c r="Y43" s="2" t="inlineStr"/>
       <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4003,11 +4134,14 @@
       <c r="U44" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W44" s="2" t="inlineStr"/>
       <c r="X44" s="2" t="inlineStr"/>
       <c r="Y44" s="2" t="inlineStr"/>
       <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4077,11 +4211,14 @@
       <c r="U45" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W45" s="2" t="inlineStr"/>
       <c r="X45" s="2" t="inlineStr"/>
       <c r="Y45" s="2" t="inlineStr"/>
       <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4151,11 +4288,14 @@
       <c r="U46" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W46" s="2" t="inlineStr"/>
       <c r="X46" s="2" t="inlineStr"/>
       <c r="Y46" s="2" t="inlineStr"/>
       <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4229,11 +4369,14 @@
       <c r="U47" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W47" s="2" t="inlineStr"/>
       <c r="X47" s="2" t="inlineStr"/>
       <c r="Y47" s="2" t="inlineStr"/>
       <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4303,11 +4446,14 @@
       <c r="U48" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W48" s="2" t="inlineStr"/>
       <c r="X48" s="2" t="inlineStr"/>
       <c r="Y48" s="2" t="inlineStr"/>
       <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4377,11 +4523,14 @@
       <c r="U49" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W49" s="2" t="inlineStr"/>
       <c r="X49" s="2" t="inlineStr"/>
       <c r="Y49" s="2" t="inlineStr"/>
       <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4451,11 +4600,14 @@
       <c r="U50" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W50" s="2" t="inlineStr"/>
       <c r="X50" s="2" t="inlineStr"/>
       <c r="Y50" s="2" t="inlineStr"/>
       <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4525,11 +4677,14 @@
       <c r="U51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W51" s="2" t="inlineStr"/>
       <c r="X51" s="2" t="inlineStr"/>
       <c r="Y51" s="2" t="inlineStr"/>
       <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4599,11 +4754,14 @@
       <c r="U52" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W52" s="2" t="inlineStr"/>
       <c r="X52" s="2" t="inlineStr"/>
       <c r="Y52" s="2" t="inlineStr"/>
       <c r="Z52" s="2" t="inlineStr"/>
+      <c r="AA52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4681,11 +4839,14 @@
       <c r="U53" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W53" s="2" t="inlineStr"/>
       <c r="X53" s="2" t="inlineStr"/>
       <c r="Y53" s="2" t="inlineStr"/>
       <c r="Z53" s="2" t="inlineStr"/>
+      <c r="AA53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4763,11 +4924,14 @@
       <c r="U54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W54" s="2" t="inlineStr"/>
       <c r="X54" s="2" t="inlineStr"/>
       <c r="Y54" s="2" t="inlineStr"/>
       <c r="Z54" s="2" t="inlineStr"/>
+      <c r="AA54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -4849,11 +5013,14 @@
       <c r="U55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W55" s="2" t="inlineStr"/>
       <c r="X55" s="2" t="inlineStr"/>
       <c r="Y55" s="2" t="inlineStr"/>
       <c r="Z55" s="2" t="inlineStr"/>
+      <c r="AA55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4935,13 +5102,16 @@
       <c r="U56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W56" s="2" t="inlineStr"/>
-      <c r="X56" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr"/>
+      <c r="Y56" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Z56" s="2" t="inlineStr"/>
+      <c r="AA56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5011,11 +5181,14 @@
       <c r="U57" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W57" s="2" t="inlineStr"/>
       <c r="X57" s="2" t="inlineStr"/>
       <c r="Y57" s="2" t="inlineStr"/>
       <c r="Z57" s="2" t="inlineStr"/>
+      <c r="AA57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5085,11 +5258,14 @@
       <c r="U58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W58" s="2" t="inlineStr"/>
       <c r="X58" s="2" t="inlineStr"/>
       <c r="Y58" s="2" t="inlineStr"/>
       <c r="Z58" s="2" t="inlineStr"/>
+      <c r="AA58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5175,11 +5351,14 @@
       <c r="U59" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W59" s="2" t="inlineStr"/>
       <c r="X59" s="2" t="inlineStr"/>
       <c r="Y59" s="2" t="inlineStr"/>
       <c r="Z59" s="2" t="inlineStr"/>
+      <c r="AA59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5255,13 +5434,16 @@
         <v>0</v>
       </c>
       <c r="U60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W60" s="2" t="inlineStr"/>
       <c r="X60" s="2" t="inlineStr"/>
       <c r="Y60" s="2" t="inlineStr"/>
       <c r="Z60" s="2" t="inlineStr"/>
+      <c r="AA60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5351,19 +5533,22 @@
       <c r="U61" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="2" t="inlineStr">
+      <c r="V61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
         <is>
           <t>화문석</t>
         </is>
       </c>
-      <c r="W61" s="2" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr">
         <is>
           <t>마니산 참성단</t>
         </is>
       </c>
-      <c r="X61" s="2" t="inlineStr"/>
       <c r="Y61" s="2" t="inlineStr"/>
       <c r="Z61" s="2" t="inlineStr"/>
+      <c r="AA61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5437,11 +5622,14 @@
       <c r="U62" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W62" s="2" t="inlineStr"/>
       <c r="X62" s="2" t="inlineStr"/>
       <c r="Y62" s="2" t="inlineStr"/>
       <c r="Z62" s="2" t="inlineStr"/>
+      <c r="AA62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5515,11 +5703,14 @@
       <c r="U63" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W63" s="2" t="inlineStr"/>
       <c r="X63" s="2" t="inlineStr"/>
       <c r="Y63" s="2" t="inlineStr"/>
       <c r="Z63" s="2" t="inlineStr"/>
+      <c r="AA63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5593,11 +5784,14 @@
       <c r="U64" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W64" s="2" t="inlineStr"/>
       <c r="X64" s="2" t="inlineStr"/>
       <c r="Y64" s="2" t="inlineStr"/>
       <c r="Z64" s="2" t="inlineStr"/>
+      <c r="AA64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5671,11 +5865,14 @@
       <c r="U65" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W65" s="2" t="inlineStr"/>
       <c r="X65" s="2" t="inlineStr"/>
       <c r="Y65" s="2" t="inlineStr"/>
       <c r="Z65" s="2" t="inlineStr"/>
+      <c r="AA65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -5745,11 +5942,14 @@
       <c r="U66" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W66" s="2" t="inlineStr"/>
       <c r="X66" s="2" t="inlineStr"/>
       <c r="Y66" s="2" t="inlineStr"/>
       <c r="Z66" s="2" t="inlineStr"/>
+      <c r="AA66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -5819,11 +6019,14 @@
       <c r="U67" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W67" s="2" t="inlineStr"/>
       <c r="X67" s="2" t="inlineStr"/>
       <c r="Y67" s="2" t="inlineStr"/>
       <c r="Z67" s="2" t="inlineStr"/>
+      <c r="AA67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -5897,11 +6100,14 @@
       <c r="U68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W68" s="2" t="inlineStr"/>
       <c r="X68" s="2" t="inlineStr"/>
       <c r="Y68" s="2" t="inlineStr"/>
       <c r="Z68" s="2" t="inlineStr"/>
+      <c r="AA68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -5971,15 +6177,18 @@
       <c r="U69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V69" s="2" t="inlineStr">
+      <c r="V69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>성심당 빵</t>
         </is>
       </c>
-      <c r="W69" s="2" t="inlineStr"/>
       <c r="X69" s="2" t="inlineStr"/>
       <c r="Y69" s="2" t="inlineStr"/>
       <c r="Z69" s="2" t="inlineStr"/>
+      <c r="AA69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -6053,11 +6262,14 @@
       <c r="U70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W70" s="2" t="inlineStr"/>
       <c r="X70" s="2" t="inlineStr"/>
       <c r="Y70" s="2" t="inlineStr"/>
       <c r="Z70" s="2" t="inlineStr"/>
+      <c r="AA70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -6131,11 +6343,14 @@
       <c r="U71" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W71" s="2" t="inlineStr"/>
       <c r="X71" s="2" t="inlineStr"/>
       <c r="Y71" s="2" t="inlineStr"/>
-      <c r="Z71" s="2" t="inlineStr">
+      <c r="Z71" s="2" t="inlineStr"/>
+      <c r="AA71" s="2" t="inlineStr">
         <is>
           <t>1 (수력(대청댐))</t>
         </is>
@@ -6217,13 +6432,16 @@
       <c r="U72" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W72" s="2" t="inlineStr"/>
-      <c r="X72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr"/>
+      <c r="Y72" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Z72" s="2" t="inlineStr"/>
+      <c r="AA72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -6305,17 +6523,20 @@
       <c r="U73" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="2" t="inlineStr">
+      <c r="V73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>언양 불고기</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr"/>
-      <c r="X73" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y73" s="2" t="inlineStr"/>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr"/>
+      <c r="Y73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z73" s="2" t="inlineStr"/>
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>2 (원자력(새울))</t>
         </is>
@@ -6397,11 +6618,14 @@
       <c r="U74" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W74" s="2" t="inlineStr"/>
       <c r="X74" s="2" t="inlineStr"/>
       <c r="Y74" s="2" t="inlineStr"/>
       <c r="Z74" s="2" t="inlineStr"/>
+      <c r="AA74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -6471,11 +6695,14 @@
       <c r="U75" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W75" s="2" t="inlineStr"/>
       <c r="X75" s="2" t="inlineStr"/>
       <c r="Y75" s="2" t="inlineStr"/>
       <c r="Z75" s="2" t="inlineStr"/>
+      <c r="AA75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -6551,17 +6778,20 @@
         <v>0</v>
       </c>
       <c r="U76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" s="2" t="inlineStr"/>
-      <c r="W76" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W76" s="2" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr">
         <is>
           <t>대왕암</t>
         </is>
       </c>
-      <c r="X76" s="2" t="inlineStr"/>
       <c r="Y76" s="2" t="inlineStr"/>
       <c r="Z76" s="2" t="inlineStr"/>
+      <c r="AA76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -6635,15 +6865,18 @@
       <c r="U77" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="2" t="inlineStr">
+      <c r="V77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
         <is>
           <t>세종 복숭아</t>
         </is>
       </c>
-      <c r="W77" s="2" t="inlineStr"/>
       <c r="X77" s="2" t="inlineStr"/>
       <c r="Y77" s="2" t="inlineStr"/>
       <c r="Z77" s="2" t="inlineStr"/>
+      <c r="AA77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -6713,15 +6946,18 @@
       <c r="U78" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="2" t="inlineStr">
+      <c r="V78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
         <is>
           <t>왕갈비</t>
         </is>
       </c>
-      <c r="W78" s="2" t="inlineStr"/>
       <c r="X78" s="2" t="inlineStr"/>
       <c r="Y78" s="2" t="inlineStr"/>
       <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -6791,11 +7027,14 @@
       <c r="U79" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W79" s="2" t="inlineStr"/>
       <c r="X79" s="2" t="inlineStr"/>
       <c r="Y79" s="2" t="inlineStr"/>
       <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -6869,15 +7108,18 @@
       <c r="U80" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V80" s="2" t="inlineStr"/>
-      <c r="W80" s="2" t="inlineStr">
+      <c r="V80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr">
         <is>
           <t>북한산 백운대</t>
         </is>
       </c>
-      <c r="X80" s="2" t="inlineStr"/>
       <c r="Y80" s="2" t="inlineStr"/>
       <c r="Z80" s="2" t="inlineStr"/>
+      <c r="AA80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -6955,11 +7197,14 @@
       <c r="U81" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W81" s="2" t="inlineStr"/>
       <c r="X81" s="2" t="inlineStr"/>
       <c r="Y81" s="2" t="inlineStr"/>
       <c r="Z81" s="2" t="inlineStr"/>
+      <c r="AA81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -7029,11 +7274,14 @@
       <c r="U82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W82" s="2" t="inlineStr"/>
       <c r="X82" s="2" t="inlineStr"/>
       <c r="Y82" s="2" t="inlineStr"/>
       <c r="Z82" s="2" t="inlineStr"/>
+      <c r="AA82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -7103,11 +7351,14 @@
       <c r="U83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W83" s="2" t="inlineStr"/>
       <c r="X83" s="2" t="inlineStr"/>
       <c r="Y83" s="2" t="inlineStr"/>
       <c r="Z83" s="2" t="inlineStr"/>
+      <c r="AA83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -7181,15 +7432,18 @@
       <c r="U84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="2" t="inlineStr">
+      <c r="V84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
         <is>
           <t>먹골배</t>
         </is>
       </c>
-      <c r="W84" s="2" t="inlineStr"/>
       <c r="X84" s="2" t="inlineStr"/>
       <c r="Y84" s="2" t="inlineStr"/>
-      <c r="Z84" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr"/>
+      <c r="AA84" s="2" t="inlineStr">
         <is>
           <t>1 (수력(팔당댐))</t>
         </is>
@@ -7269,13 +7523,16 @@
         <v>0</v>
       </c>
       <c r="U85" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" s="2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="V85" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W85" s="2" t="inlineStr"/>
       <c r="X85" s="2" t="inlineStr"/>
       <c r="Y85" s="2" t="inlineStr"/>
       <c r="Z85" s="2" t="inlineStr"/>
+      <c r="AA85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -7357,11 +7614,14 @@
       <c r="U86" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W86" s="2" t="inlineStr"/>
       <c r="X86" s="2" t="inlineStr"/>
       <c r="Y86" s="2" t="inlineStr"/>
       <c r="Z86" s="2" t="inlineStr"/>
+      <c r="AA86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -7431,11 +7691,14 @@
       <c r="U87" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W87" s="2" t="inlineStr"/>
       <c r="X87" s="2" t="inlineStr"/>
       <c r="Y87" s="2" t="inlineStr"/>
       <c r="Z87" s="2" t="inlineStr"/>
+      <c r="AA87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -7509,15 +7772,18 @@
       <c r="U88" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W88" s="2" t="inlineStr"/>
       <c r="X88" s="2" t="inlineStr"/>
-      <c r="Y88" s="2" t="inlineStr">
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z88" s="2" t="inlineStr"/>
+      <c r="AA88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -7595,11 +7861,14 @@
       <c r="U89" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W89" s="2" t="inlineStr"/>
       <c r="X89" s="2" t="inlineStr"/>
       <c r="Y89" s="2" t="inlineStr"/>
       <c r="Z89" s="2" t="inlineStr"/>
+      <c r="AA89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -7685,15 +7954,18 @@
       <c r="U90" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="2" t="inlineStr">
+      <c r="V90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>김포 쌀</t>
         </is>
       </c>
-      <c r="W90" s="2" t="inlineStr"/>
       <c r="X90" s="2" t="inlineStr"/>
       <c r="Y90" s="2" t="inlineStr"/>
       <c r="Z90" s="2" t="inlineStr"/>
+      <c r="AA90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -7763,11 +8035,14 @@
       <c r="U91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W91" s="2" t="inlineStr"/>
       <c r="X91" s="2" t="inlineStr"/>
       <c r="Y91" s="2" t="inlineStr"/>
       <c r="Z91" s="2" t="inlineStr"/>
+      <c r="AA91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -7841,11 +8116,14 @@
       <c r="U92" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W92" s="2" t="inlineStr"/>
       <c r="X92" s="2" t="inlineStr"/>
       <c r="Y92" s="2" t="inlineStr"/>
       <c r="Z92" s="2" t="inlineStr"/>
+      <c r="AA92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -7919,11 +8197,14 @@
       <c r="U93" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W93" s="2" t="inlineStr"/>
       <c r="X93" s="2" t="inlineStr"/>
       <c r="Y93" s="2" t="inlineStr"/>
       <c r="Z93" s="2" t="inlineStr"/>
+      <c r="AA93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -7993,11 +8274,14 @@
       <c r="U94" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W94" s="2" t="inlineStr"/>
       <c r="X94" s="2" t="inlineStr"/>
       <c r="Y94" s="2" t="inlineStr"/>
       <c r="Z94" s="2" t="inlineStr"/>
+      <c r="AA94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -8067,11 +8351,14 @@
       <c r="U95" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W95" s="2" t="inlineStr"/>
       <c r="X95" s="2" t="inlineStr"/>
       <c r="Y95" s="2" t="inlineStr"/>
       <c r="Z95" s="2" t="inlineStr"/>
+      <c r="AA95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -8141,11 +8428,14 @@
       <c r="U96" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W96" s="2" t="inlineStr"/>
       <c r="X96" s="2" t="inlineStr"/>
       <c r="Y96" s="2" t="inlineStr"/>
       <c r="Z96" s="2" t="inlineStr"/>
+      <c r="AA96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -8215,11 +8505,14 @@
       <c r="U97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W97" s="2" t="inlineStr"/>
       <c r="X97" s="2" t="inlineStr"/>
       <c r="Y97" s="2" t="inlineStr"/>
       <c r="Z97" s="2" t="inlineStr"/>
+      <c r="AA97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -8293,15 +8586,18 @@
       <c r="U98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="2" t="inlineStr">
+      <c r="V98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
         <is>
           <t>이천 쌀</t>
         </is>
       </c>
-      <c r="W98" s="2" t="inlineStr"/>
       <c r="X98" s="2" t="inlineStr"/>
       <c r="Y98" s="2" t="inlineStr"/>
       <c r="Z98" s="2" t="inlineStr"/>
+      <c r="AA98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -8375,15 +8671,18 @@
       <c r="U99" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="V99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
         <is>
           <t>유기</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr"/>
       <c r="X99" s="2" t="inlineStr"/>
       <c r="Y99" s="2" t="inlineStr"/>
       <c r="Z99" s="2" t="inlineStr"/>
+      <c r="AA99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -8457,11 +8756,14 @@
       <c r="U100" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W100" s="2" t="inlineStr"/>
       <c r="X100" s="2" t="inlineStr"/>
       <c r="Y100" s="2" t="inlineStr"/>
       <c r="Z100" s="2" t="inlineStr"/>
+      <c r="AA100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -8531,11 +8833,14 @@
       <c r="U101" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W101" s="2" t="inlineStr"/>
       <c r="X101" s="2" t="inlineStr"/>
       <c r="Y101" s="2" t="inlineStr"/>
       <c r="Z101" s="2" t="inlineStr"/>
+      <c r="AA101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -8605,15 +8910,18 @@
       <c r="U102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V102" s="2" t="inlineStr">
+      <c r="V102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
         <is>
           <t>이동갈비</t>
         </is>
       </c>
-      <c r="W102" s="2" t="inlineStr"/>
       <c r="X102" s="2" t="inlineStr"/>
       <c r="Y102" s="2" t="inlineStr"/>
       <c r="Z102" s="2" t="inlineStr"/>
+      <c r="AA102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -8687,19 +8995,22 @@
       <c r="U103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V103" s="2" t="inlineStr">
+      <c r="V103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
         <is>
           <t>해장국</t>
         </is>
       </c>
-      <c r="W103" s="2" t="inlineStr">
+      <c r="X103" s="2" t="inlineStr">
         <is>
           <t>두물머리</t>
         </is>
       </c>
-      <c r="X103" s="2" t="inlineStr"/>
       <c r="Y103" s="2" t="inlineStr"/>
       <c r="Z103" s="2" t="inlineStr"/>
+      <c r="AA103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -8773,15 +9084,18 @@
       <c r="U104" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V104" s="2" t="inlineStr">
+      <c r="V104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
         <is>
           <t>여주 쌀</t>
         </is>
       </c>
-      <c r="W104" s="2" t="inlineStr"/>
       <c r="X104" s="2" t="inlineStr"/>
       <c r="Y104" s="2" t="inlineStr"/>
       <c r="Z104" s="2" t="inlineStr"/>
+      <c r="AA104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -8851,11 +9165,14 @@
       <c r="U105" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="2" t="inlineStr"/>
+      <c r="V105" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W105" s="2" t="inlineStr"/>
       <c r="X105" s="2" t="inlineStr"/>
       <c r="Y105" s="2" t="inlineStr"/>
       <c r="Z105" s="2" t="inlineStr"/>
+      <c r="AA105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -8925,11 +9242,14 @@
       <c r="U106" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V106" s="2" t="inlineStr"/>
+      <c r="V106" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W106" s="2" t="inlineStr"/>
       <c r="X106" s="2" t="inlineStr"/>
       <c r="Y106" s="2" t="inlineStr"/>
       <c r="Z106" s="2" t="inlineStr"/>
+      <c r="AA106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -9003,15 +9323,18 @@
       <c r="U107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="2" t="inlineStr">
+      <c r="V107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
         <is>
           <t>가평 잣</t>
         </is>
       </c>
-      <c r="W107" s="2" t="inlineStr"/>
       <c r="X107" s="2" t="inlineStr"/>
       <c r="Y107" s="2" t="inlineStr"/>
-      <c r="Z107" s="2" t="inlineStr">
+      <c r="Z107" s="2" t="inlineStr"/>
+      <c r="AA107" s="2" t="inlineStr">
         <is>
           <t>1 (수력(청평댐))</t>
         </is>
@@ -9089,15 +9412,18 @@
       <c r="U108" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V108" s="2" t="inlineStr">
+      <c r="V108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
         <is>
           <t>율무</t>
         </is>
       </c>
-      <c r="W108" s="2" t="inlineStr"/>
       <c r="X108" s="2" t="inlineStr"/>
       <c r="Y108" s="2" t="inlineStr"/>
       <c r="Z108" s="2" t="inlineStr"/>
+      <c r="AA108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -9171,19 +9497,22 @@
       <c r="U109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V109" s="2" t="inlineStr">
+      <c r="V109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" s="2" t="inlineStr">
         <is>
           <t>원주 복숭아</t>
         </is>
       </c>
-      <c r="W109" s="2" t="inlineStr"/>
       <c r="X109" s="2" t="inlineStr"/>
-      <c r="Y109" s="2" t="inlineStr">
+      <c r="Y109" s="2" t="inlineStr"/>
+      <c r="Z109" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z109" s="2" t="inlineStr"/>
+      <c r="AA109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -9257,19 +9586,22 @@
       <c r="U110" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="2" t="inlineStr">
+      <c r="V110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
         <is>
           <t>닭갈비</t>
         </is>
       </c>
-      <c r="W110" s="2" t="inlineStr">
+      <c r="X110" s="2" t="inlineStr">
         <is>
           <t>소양호</t>
         </is>
       </c>
-      <c r="X110" s="2" t="inlineStr"/>
       <c r="Y110" s="2" t="inlineStr"/>
-      <c r="Z110" s="2" t="inlineStr">
+      <c r="Z110" s="2" t="inlineStr"/>
+      <c r="AA110" s="2" t="inlineStr">
         <is>
           <t>1 (수력(소양강댐))</t>
         </is>
@@ -9355,23 +9687,26 @@
       <c r="U111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="2" t="inlineStr">
+      <c r="V111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
         <is>
           <t>초당두부</t>
         </is>
       </c>
-      <c r="W111" s="2" t="inlineStr">
+      <c r="X111" s="2" t="inlineStr">
         <is>
           <t>정동진</t>
         </is>
       </c>
-      <c r="X111" s="2" t="inlineStr"/>
-      <c r="Y111" s="2" t="inlineStr">
+      <c r="Y111" s="2" t="inlineStr"/>
+      <c r="Z111" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z111" s="2" t="inlineStr"/>
+      <c r="AA111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -9445,19 +9780,22 @@
       <c r="U112" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="2" t="inlineStr">
+      <c r="V112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="2" t="inlineStr">
         <is>
           <t>오대쌀</t>
         </is>
       </c>
-      <c r="W112" s="2" t="inlineStr">
+      <c r="X112" s="2" t="inlineStr">
         <is>
           <t>한탄강 주상절리</t>
         </is>
       </c>
-      <c r="X112" s="2" t="inlineStr"/>
       <c r="Y112" s="2" t="inlineStr"/>
       <c r="Z112" s="2" t="inlineStr"/>
+      <c r="AA112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -9539,15 +9877,18 @@
       <c r="U113" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="2" t="inlineStr"/>
-      <c r="W113" s="2" t="inlineStr">
+      <c r="V113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W113" s="2" t="inlineStr"/>
+      <c r="X113" s="2" t="inlineStr">
         <is>
           <t>해금강</t>
         </is>
       </c>
-      <c r="X113" s="2" t="inlineStr"/>
       <c r="Y113" s="2" t="inlineStr"/>
       <c r="Z113" s="2" t="inlineStr"/>
+      <c r="AA113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -9629,19 +9970,22 @@
       <c r="U114" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V114" s="2" t="inlineStr"/>
-      <c r="W114" s="2" t="inlineStr">
+      <c r="V114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W114" s="2" t="inlineStr"/>
+      <c r="X114" s="2" t="inlineStr">
         <is>
           <t>추암 촛대바위</t>
         </is>
       </c>
-      <c r="X114" s="2" t="inlineStr"/>
-      <c r="Y114" s="2" t="inlineStr">
+      <c r="Y114" s="2" t="inlineStr"/>
+      <c r="Z114" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z114" s="2" t="inlineStr"/>
+      <c r="AA114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -9723,19 +10067,22 @@
       <c r="U115" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V115" s="2" t="inlineStr">
+      <c r="V115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W115" s="2" t="inlineStr">
         <is>
           <t>속초 오징어</t>
         </is>
       </c>
-      <c r="W115" s="2" t="inlineStr">
+      <c r="X115" s="2" t="inlineStr">
         <is>
           <t>청초호</t>
         </is>
       </c>
-      <c r="X115" s="2" t="inlineStr"/>
       <c r="Y115" s="2" t="inlineStr"/>
       <c r="Z115" s="2" t="inlineStr"/>
+      <c r="AA115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -9809,19 +10156,22 @@
       <c r="U116" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V116" s="2" t="inlineStr">
+      <c r="V116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="2" t="inlineStr">
         <is>
           <t>찰옥수수</t>
         </is>
       </c>
-      <c r="W116" s="2" t="inlineStr"/>
       <c r="X116" s="2" t="inlineStr"/>
-      <c r="Y116" s="2" t="inlineStr">
+      <c r="Y116" s="2" t="inlineStr"/>
+      <c r="Z116" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z116" s="2" t="inlineStr"/>
+      <c r="AA116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -9903,15 +10253,18 @@
       <c r="U117" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="2" t="inlineStr"/>
+      <c r="V117" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W117" s="2" t="inlineStr"/>
       <c r="X117" s="2" t="inlineStr"/>
-      <c r="Y117" s="2" t="inlineStr">
+      <c r="Y117" s="2" t="inlineStr"/>
+      <c r="Z117" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z117" s="2" t="inlineStr"/>
+      <c r="AA117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -9985,15 +10338,18 @@
       <c r="U118" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V118" s="2" t="inlineStr">
+      <c r="V118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W118" s="2" t="inlineStr">
         <is>
           <t>한우</t>
         </is>
       </c>
-      <c r="W118" s="2" t="inlineStr"/>
       <c r="X118" s="2" t="inlineStr"/>
       <c r="Y118" s="2" t="inlineStr"/>
       <c r="Z118" s="2" t="inlineStr"/>
+      <c r="AA118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -10067,19 +10423,22 @@
       <c r="U119" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V119" s="2" t="inlineStr">
+      <c r="V119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W119" s="2" t="inlineStr">
         <is>
           <t>송어</t>
         </is>
       </c>
-      <c r="W119" s="2" t="inlineStr"/>
       <c r="X119" s="2" t="inlineStr"/>
-      <c r="Y119" s="2" t="inlineStr">
+      <c r="Y119" s="2" t="inlineStr"/>
+      <c r="Z119" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z119" s="2" t="inlineStr"/>
+      <c r="AA119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -10153,19 +10512,22 @@
       <c r="U120" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="2" t="inlineStr">
+      <c r="V120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="2" t="inlineStr">
         <is>
           <t>고랭지배추</t>
         </is>
       </c>
-      <c r="W120" s="2" t="inlineStr"/>
       <c r="X120" s="2" t="inlineStr"/>
-      <c r="Y120" s="2" t="inlineStr">
+      <c r="Y120" s="2" t="inlineStr"/>
+      <c r="Z120" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z120" s="2" t="inlineStr"/>
+      <c r="AA120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -10239,23 +10601,26 @@
       <c r="U121" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="2" t="inlineStr">
+      <c r="V121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="2" t="inlineStr">
         <is>
           <t>곤드레</t>
         </is>
       </c>
-      <c r="W121" s="2" t="inlineStr">
+      <c r="X121" s="2" t="inlineStr">
         <is>
           <t>한반도지형</t>
         </is>
       </c>
-      <c r="X121" s="2" t="inlineStr"/>
-      <c r="Y121" s="2" t="inlineStr">
+      <c r="Y121" s="2" t="inlineStr"/>
+      <c r="Z121" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z121" s="2" t="inlineStr"/>
+      <c r="AA121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -10329,15 +10694,18 @@
       <c r="U122" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="2" t="inlineStr"/>
+      <c r="V122" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W122" s="2" t="inlineStr"/>
       <c r="X122" s="2" t="inlineStr"/>
-      <c r="Y122" s="2" t="inlineStr">
+      <c r="Y122" s="2" t="inlineStr"/>
+      <c r="Z122" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z122" s="2" t="inlineStr"/>
+      <c r="AA122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -10411,15 +10779,18 @@
       <c r="U123" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="2" t="inlineStr"/>
-      <c r="W123" s="2" t="inlineStr">
+      <c r="V123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="2" t="inlineStr"/>
+      <c r="X123" s="2" t="inlineStr">
         <is>
           <t>설악산 대청봉</t>
         </is>
       </c>
-      <c r="X123" s="2" t="inlineStr"/>
       <c r="Y123" s="2" t="inlineStr"/>
       <c r="Z123" s="2" t="inlineStr"/>
+      <c r="AA123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -10501,15 +10872,18 @@
       <c r="U124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="2" t="inlineStr">
+      <c r="V124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" s="2" t="inlineStr">
         <is>
           <t>송이버섯</t>
         </is>
       </c>
-      <c r="W124" s="2" t="inlineStr"/>
       <c r="X124" s="2" t="inlineStr"/>
       <c r="Y124" s="2" t="inlineStr"/>
       <c r="Z124" s="2" t="inlineStr"/>
+      <c r="AA124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -10583,15 +10957,18 @@
       <c r="U125" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="2" t="inlineStr">
+      <c r="V125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W125" s="2" t="inlineStr">
         <is>
           <t>산천어</t>
         </is>
       </c>
-      <c r="W125" s="2" t="inlineStr"/>
       <c r="X125" s="2" t="inlineStr"/>
       <c r="Y125" s="2" t="inlineStr"/>
-      <c r="Z125" s="2" t="inlineStr">
+      <c r="Z125" s="2" t="inlineStr"/>
+      <c r="AA125" s="2" t="inlineStr">
         <is>
           <t>1 (수력(화천댐))</t>
         </is>
@@ -10669,11 +11046,14 @@
       <c r="U126" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="2" t="inlineStr"/>
+      <c r="V126" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W126" s="2" t="inlineStr"/>
       <c r="X126" s="2" t="inlineStr"/>
       <c r="Y126" s="2" t="inlineStr"/>
       <c r="Z126" s="2" t="inlineStr"/>
+      <c r="AA126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -10749,21 +11129,24 @@
         <v>0</v>
       </c>
       <c r="U127" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W127" s="2" t="inlineStr">
         <is>
           <t>명태</t>
         </is>
       </c>
-      <c r="W127" s="2" t="inlineStr">
+      <c r="X127" s="2" t="inlineStr">
         <is>
           <t>명사십리</t>
         </is>
       </c>
-      <c r="X127" s="2" t="inlineStr"/>
       <c r="Y127" s="2" t="inlineStr"/>
       <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -10841,15 +11224,18 @@
       <c r="U128" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W128" s="2" t="inlineStr"/>
       <c r="X128" s="2" t="inlineStr"/>
-      <c r="Y128" s="2" t="inlineStr">
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -10923,11 +11309,14 @@
       <c r="U129" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W129" s="2" t="inlineStr"/>
       <c r="X129" s="2" t="inlineStr"/>
       <c r="Y129" s="2" t="inlineStr"/>
       <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -11009,11 +11398,14 @@
       <c r="U130" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W130" s="2" t="inlineStr"/>
       <c r="X130" s="2" t="inlineStr"/>
       <c r="Y130" s="2" t="inlineStr"/>
-      <c r="Z130" s="2" t="inlineStr">
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr">
         <is>
           <t>1 (수력(안변청년))</t>
         </is>
@@ -11091,11 +11483,14 @@
       <c r="U131" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W131" s="2" t="inlineStr"/>
       <c r="X131" s="2" t="inlineStr"/>
       <c r="Y131" s="2" t="inlineStr"/>
       <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -11177,19 +11572,22 @@
       <c r="U132" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="2" t="inlineStr">
+      <c r="V132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" s="2" t="inlineStr">
         <is>
           <t>문어</t>
         </is>
       </c>
-      <c r="W132" s="2" t="inlineStr">
+      <c r="X132" s="2" t="inlineStr">
         <is>
           <t>총석정</t>
         </is>
       </c>
-      <c r="X132" s="2" t="inlineStr"/>
       <c r="Y132" s="2" t="inlineStr"/>
       <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -11267,15 +11665,18 @@
       <c r="U133" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="2" t="inlineStr"/>
+      <c r="V133" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W133" s="2" t="inlineStr"/>
       <c r="X133" s="2" t="inlineStr"/>
-      <c r="Y133" s="2" t="inlineStr">
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -11349,11 +11750,14 @@
       <c r="U134" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="2" t="inlineStr"/>
+      <c r="V134" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W134" s="2" t="inlineStr"/>
       <c r="X134" s="2" t="inlineStr"/>
       <c r="Y134" s="2" t="inlineStr"/>
       <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -11427,11 +11831,14 @@
       <c r="U135" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W135" s="2" t="inlineStr"/>
       <c r="X135" s="2" t="inlineStr"/>
       <c r="Y135" s="2" t="inlineStr"/>
       <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -11505,11 +11912,14 @@
       <c r="U136" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W136" s="2" t="inlineStr"/>
       <c r="X136" s="2" t="inlineStr"/>
       <c r="Y136" s="2" t="inlineStr"/>
       <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -11583,15 +11993,18 @@
       <c r="U137" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V137" s="2" t="inlineStr"/>
-      <c r="W137" s="2" t="inlineStr">
+      <c r="V137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" s="2" t="inlineStr"/>
+      <c r="X137" s="2" t="inlineStr">
         <is>
           <t>금강산 만물상</t>
         </is>
       </c>
-      <c r="X137" s="2" t="inlineStr"/>
       <c r="Y137" s="2" t="inlineStr"/>
       <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -11665,15 +12078,18 @@
       <c r="U138" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="2" t="inlineStr"/>
-      <c r="W138" s="2" t="inlineStr">
+      <c r="V138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" s="2" t="inlineStr"/>
+      <c r="X138" s="2" t="inlineStr">
         <is>
           <t>외금강</t>
         </is>
       </c>
-      <c r="X138" s="2" t="inlineStr"/>
       <c r="Y138" s="2" t="inlineStr"/>
       <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -11747,11 +12163,14 @@
       <c r="U139" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W139" s="2" t="inlineStr"/>
       <c r="X139" s="2" t="inlineStr"/>
       <c r="Y139" s="2" t="inlineStr"/>
       <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -11825,15 +12244,18 @@
       <c r="U140" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V140" s="2" t="inlineStr">
+      <c r="V140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" s="2" t="inlineStr">
         <is>
           <t>송이</t>
         </is>
       </c>
-      <c r="W140" s="2" t="inlineStr"/>
       <c r="X140" s="2" t="inlineStr"/>
       <c r="Y140" s="2" t="inlineStr"/>
       <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -11907,11 +12329,14 @@
       <c r="U141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W141" s="2" t="inlineStr"/>
       <c r="X141" s="2" t="inlineStr"/>
       <c r="Y141" s="2" t="inlineStr"/>
       <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -11985,11 +12410,14 @@
       <c r="U142" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W142" s="2" t="inlineStr"/>
       <c r="X142" s="2" t="inlineStr"/>
       <c r="Y142" s="2" t="inlineStr"/>
       <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -12063,23 +12491,26 @@
       <c r="U143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V143" s="2" t="inlineStr">
+      <c r="V143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" s="2" t="inlineStr">
         <is>
           <t>충주 사과</t>
         </is>
       </c>
-      <c r="W143" s="2" t="inlineStr">
+      <c r="X143" s="2" t="inlineStr">
         <is>
           <t>충주호</t>
         </is>
       </c>
-      <c r="X143" s="2" t="inlineStr"/>
-      <c r="Y143" s="2" t="inlineStr">
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z143" s="2" t="inlineStr">
+      <c r="AA143" s="2" t="inlineStr">
         <is>
           <t>1 (수력(충주댐))</t>
         </is>
@@ -12157,19 +12588,22 @@
       <c r="U144" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V144" s="2" t="inlineStr"/>
-      <c r="W144" s="2" t="inlineStr">
+      <c r="V144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" s="2" t="inlineStr"/>
+      <c r="X144" s="2" t="inlineStr">
         <is>
           <t>청풍호 옥순봉</t>
         </is>
       </c>
-      <c r="X144" s="2" t="inlineStr"/>
-      <c r="Y144" s="2" t="inlineStr">
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -12243,11 +12677,14 @@
       <c r="U145" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W145" s="2" t="inlineStr"/>
       <c r="X145" s="2" t="inlineStr"/>
       <c r="Y145" s="2" t="inlineStr"/>
       <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -12321,11 +12758,14 @@
       <c r="U146" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W146" s="2" t="inlineStr"/>
       <c r="X146" s="2" t="inlineStr"/>
       <c r="Y146" s="2" t="inlineStr"/>
       <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -12399,19 +12839,22 @@
       <c r="U147" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V147" s="2" t="inlineStr"/>
-      <c r="W147" s="2" t="inlineStr">
+      <c r="V147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" s="2" t="inlineStr"/>
+      <c r="X147" s="2" t="inlineStr">
         <is>
           <t>부소담악</t>
         </is>
       </c>
-      <c r="X147" s="2" t="inlineStr"/>
-      <c r="Y147" s="2" t="inlineStr">
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -12485,19 +12928,22 @@
       <c r="U148" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V148" s="2" t="inlineStr">
+      <c r="V148" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" s="2" t="inlineStr">
         <is>
           <t>영동 포도</t>
         </is>
       </c>
-      <c r="W148" s="2" t="inlineStr"/>
       <c r="X148" s="2" t="inlineStr"/>
-      <c r="Y148" s="2" t="inlineStr">
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -12571,15 +13017,18 @@
       <c r="U149" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V149" s="2" t="inlineStr">
+      <c r="V149" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" s="2" t="inlineStr">
         <is>
           <t>고추</t>
         </is>
       </c>
-      <c r="W149" s="2" t="inlineStr"/>
       <c r="X149" s="2" t="inlineStr"/>
       <c r="Y149" s="2" t="inlineStr"/>
       <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -12649,11 +13098,14 @@
       <c r="U150" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W150" s="2" t="inlineStr"/>
       <c r="X150" s="2" t="inlineStr"/>
       <c r="Y150" s="2" t="inlineStr"/>
       <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -12727,19 +13179,22 @@
       <c r="U151" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V151" s="2" t="inlineStr"/>
-      <c r="W151" s="2" t="inlineStr">
+      <c r="V151" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" s="2" t="inlineStr"/>
+      <c r="X151" s="2" t="inlineStr">
         <is>
           <t>속리산 문장대</t>
         </is>
       </c>
-      <c r="X151" s="2" t="inlineStr"/>
-      <c r="Y151" s="2" t="inlineStr">
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -12813,23 +13268,26 @@
       <c r="U152" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V152" s="2" t="inlineStr">
+      <c r="V152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" s="2" t="inlineStr">
         <is>
           <t>단양 마늘</t>
         </is>
       </c>
-      <c r="W152" s="2" t="inlineStr">
+      <c r="X152" s="2" t="inlineStr">
         <is>
           <t>도담삼봉</t>
         </is>
       </c>
-      <c r="X152" s="2" t="inlineStr"/>
-      <c r="Y152" s="2" t="inlineStr">
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -12903,15 +13361,18 @@
       <c r="U153" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V153" s="2" t="inlineStr">
+      <c r="V153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" s="2" t="inlineStr">
         <is>
           <t>호두과자</t>
         </is>
       </c>
-      <c r="W153" s="2" t="inlineStr"/>
       <c r="X153" s="2" t="inlineStr"/>
       <c r="Y153" s="2" t="inlineStr"/>
       <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -12993,11 +13454,14 @@
       <c r="U154" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W154" s="2" t="inlineStr"/>
       <c r="X154" s="2" t="inlineStr"/>
       <c r="Y154" s="2" t="inlineStr"/>
       <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -13075,11 +13539,14 @@
       <c r="U155" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W155" s="2" t="inlineStr"/>
       <c r="X155" s="2" t="inlineStr"/>
       <c r="Y155" s="2" t="inlineStr"/>
       <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -13157,13 +13624,16 @@
       <c r="U156" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W156" s="2" t="inlineStr"/>
-      <c r="X156" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="X156" s="2" t="inlineStr"/>
+      <c r="Y156" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -13237,15 +13707,18 @@
       <c r="U157" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V157" s="2" t="inlineStr">
+      <c r="V157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W157" s="2" t="inlineStr">
         <is>
           <t>딸기</t>
         </is>
       </c>
-      <c r="W157" s="2" t="inlineStr"/>
       <c r="X157" s="2" t="inlineStr"/>
       <c r="Y157" s="2" t="inlineStr"/>
       <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -13327,15 +13800,18 @@
       <c r="U158" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V158" s="2" t="inlineStr">
+      <c r="V158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W158" s="2" t="inlineStr">
         <is>
           <t>새우젓</t>
         </is>
       </c>
-      <c r="W158" s="2" t="inlineStr"/>
       <c r="X158" s="2" t="inlineStr"/>
       <c r="Y158" s="2" t="inlineStr"/>
       <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -13409,19 +13885,22 @@
       <c r="U159" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V159" s="2" t="inlineStr">
+      <c r="V159" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W159" s="2" t="inlineStr">
         <is>
           <t>공주 밤</t>
         </is>
       </c>
-      <c r="W159" s="2" t="inlineStr"/>
       <c r="X159" s="2" t="inlineStr"/>
-      <c r="Y159" s="2" t="inlineStr">
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -13503,15 +13982,18 @@
       <c r="U160" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W160" s="2" t="inlineStr"/>
       <c r="X160" s="2" t="inlineStr"/>
-      <c r="Y160" s="2" t="inlineStr">
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -13585,11 +14067,14 @@
       <c r="U161" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W161" s="2" t="inlineStr"/>
       <c r="X161" s="2" t="inlineStr"/>
       <c r="Y161" s="2" t="inlineStr"/>
       <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -13667,15 +14152,18 @@
       <c r="U162" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V162" s="2" t="inlineStr">
+      <c r="V162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W162" s="2" t="inlineStr">
         <is>
           <t>대하</t>
         </is>
       </c>
-      <c r="W162" s="2" t="inlineStr"/>
       <c r="X162" s="2" t="inlineStr"/>
       <c r="Y162" s="2" t="inlineStr"/>
       <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -13749,15 +14237,18 @@
       <c r="U163" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V163" s="2" t="inlineStr"/>
-      <c r="W163" s="2" t="inlineStr">
+      <c r="V163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W163" s="2" t="inlineStr"/>
+      <c r="X163" s="2" t="inlineStr">
         <is>
           <t>낙화암</t>
         </is>
       </c>
-      <c r="X163" s="2" t="inlineStr"/>
       <c r="Y163" s="2" t="inlineStr"/>
       <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -13831,15 +14322,18 @@
       <c r="U164" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V164" s="2" t="inlineStr">
+      <c r="V164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W164" s="2" t="inlineStr">
         <is>
           <t>금산 인삼</t>
         </is>
       </c>
-      <c r="W164" s="2" t="inlineStr"/>
       <c r="X164" s="2" t="inlineStr"/>
       <c r="Y164" s="2" t="inlineStr"/>
       <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -13921,15 +14415,18 @@
       <c r="U165" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V165" s="2" t="inlineStr">
+      <c r="V165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W165" s="2" t="inlineStr">
         <is>
           <t>한산 소곡주</t>
         </is>
       </c>
-      <c r="W165" s="2" t="inlineStr"/>
       <c r="X165" s="2" t="inlineStr"/>
       <c r="Y165" s="2" t="inlineStr"/>
       <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -14003,11 +14500,14 @@
       <c r="U166" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W166" s="2" t="inlineStr"/>
       <c r="X166" s="2" t="inlineStr"/>
       <c r="Y166" s="2" t="inlineStr"/>
       <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -14081,15 +14581,18 @@
       <c r="U167" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W167" s="2" t="inlineStr"/>
       <c r="X167" s="2" t="inlineStr"/>
-      <c r="Y167" s="2" t="inlineStr">
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -14163,15 +14666,18 @@
       <c r="U168" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V168" s="2" t="inlineStr">
+      <c r="V168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W168" s="2" t="inlineStr">
         <is>
           <t>이강주</t>
         </is>
       </c>
-      <c r="W168" s="2" t="inlineStr"/>
       <c r="X168" s="2" t="inlineStr"/>
       <c r="Y168" s="2" t="inlineStr"/>
       <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -14245,15 +14751,18 @@
       <c r="U169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V169" s="2" t="inlineStr">
+      <c r="V169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W169" s="2" t="inlineStr">
         <is>
           <t>보석</t>
         </is>
       </c>
-      <c r="W169" s="2" t="inlineStr"/>
       <c r="X169" s="2" t="inlineStr"/>
       <c r="Y169" s="2" t="inlineStr"/>
       <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -14337,17 +14846,20 @@
         <v>0</v>
       </c>
       <c r="U170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V170" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W170" s="2" t="inlineStr">
         <is>
           <t>찰보리쌀</t>
         </is>
       </c>
-      <c r="W170" s="2" t="inlineStr"/>
       <c r="X170" s="2" t="inlineStr"/>
       <c r="Y170" s="2" t="inlineStr"/>
       <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -14421,15 +14933,18 @@
       <c r="U171" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W171" s="2" t="inlineStr"/>
       <c r="X171" s="2" t="inlineStr"/>
-      <c r="Y171" s="2" t="inlineStr">
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -14499,15 +15014,18 @@
       <c r="U172" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W172" s="2" t="inlineStr"/>
       <c r="X172" s="2" t="inlineStr"/>
-      <c r="Y172" s="2" t="inlineStr">
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -14589,15 +15107,18 @@
       <c r="U173" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V173" s="2" t="inlineStr">
+      <c r="V173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W173" s="2" t="inlineStr">
         <is>
           <t>지평선쌀</t>
         </is>
       </c>
-      <c r="W173" s="2" t="inlineStr"/>
       <c r="X173" s="2" t="inlineStr"/>
       <c r="Y173" s="2" t="inlineStr"/>
       <c r="Z173" s="2" t="inlineStr"/>
+      <c r="AA173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -14671,15 +15192,18 @@
       <c r="U174" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V174" s="2" t="inlineStr">
+      <c r="V174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W174" s="2" t="inlineStr">
         <is>
           <t>제기</t>
         </is>
       </c>
-      <c r="W174" s="2" t="inlineStr"/>
       <c r="X174" s="2" t="inlineStr"/>
       <c r="Y174" s="2" t="inlineStr"/>
       <c r="Z174" s="2" t="inlineStr"/>
+      <c r="AA174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -14757,19 +15281,22 @@
       <c r="U175" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V175" s="2" t="inlineStr">
+      <c r="V175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W175" s="2" t="inlineStr">
         <is>
           <t>복분자</t>
         </is>
       </c>
-      <c r="W175" s="2" t="inlineStr"/>
       <c r="X175" s="2" t="inlineStr"/>
-      <c r="Y175" s="2" t="inlineStr">
+      <c r="Y175" s="2" t="inlineStr"/>
+      <c r="Z175" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z175" s="2" t="inlineStr"/>
+      <c r="AA175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -14851,19 +15378,22 @@
       <c r="U176" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V176" s="2" t="inlineStr">
+      <c r="V176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W176" s="2" t="inlineStr">
         <is>
           <t>오디</t>
         </is>
       </c>
-      <c r="W176" s="2" t="inlineStr">
+      <c r="X176" s="2" t="inlineStr">
         <is>
           <t>채석강</t>
         </is>
       </c>
-      <c r="X176" s="2" t="inlineStr"/>
       <c r="Y176" s="2" t="inlineStr"/>
       <c r="Z176" s="2" t="inlineStr"/>
+      <c r="AA176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -14937,15 +15467,18 @@
       <c r="U177" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V177" s="2" t="inlineStr">
+      <c r="V177" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W177" s="2" t="inlineStr">
         <is>
           <t>고추장</t>
         </is>
       </c>
-      <c r="W177" s="2" t="inlineStr"/>
       <c r="X177" s="2" t="inlineStr"/>
       <c r="Y177" s="2" t="inlineStr"/>
       <c r="Z177" s="2" t="inlineStr"/>
+      <c r="AA177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -15019,19 +15552,22 @@
       <c r="U178" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V178" s="2" t="inlineStr">
+      <c r="V178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W178" s="2" t="inlineStr">
         <is>
           <t>치즈</t>
         </is>
       </c>
-      <c r="W178" s="2" t="inlineStr"/>
       <c r="X178" s="2" t="inlineStr"/>
-      <c r="Y178" s="2" t="inlineStr">
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z178" s="2" t="inlineStr">
+      <c r="AA178" s="2" t="inlineStr">
         <is>
           <t>1 (수력(섬진강댐·칠보))</t>
         </is>
@@ -15109,15 +15645,18 @@
       <c r="U179" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V179" s="2" t="inlineStr"/>
-      <c r="W179" s="2" t="inlineStr">
+      <c r="V179" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W179" s="2" t="inlineStr"/>
+      <c r="X179" s="2" t="inlineStr">
         <is>
           <t>마이산 암마이봉</t>
         </is>
       </c>
-      <c r="X179" s="2" t="inlineStr"/>
       <c r="Y179" s="2" t="inlineStr"/>
       <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -15191,19 +15730,22 @@
       <c r="U180" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V180" s="2" t="inlineStr">
+      <c r="V180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W180" s="2" t="inlineStr">
         <is>
           <t>머루</t>
         </is>
       </c>
-      <c r="W180" s="2" t="inlineStr">
+      <c r="X180" s="2" t="inlineStr">
         <is>
           <t>덕유산 향적봉</t>
         </is>
       </c>
-      <c r="X180" s="2" t="inlineStr"/>
       <c r="Y180" s="2" t="inlineStr"/>
       <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -15277,11 +15819,14 @@
       <c r="U181" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W181" s="2" t="inlineStr"/>
       <c r="X181" s="2" t="inlineStr"/>
       <c r="Y181" s="2" t="inlineStr"/>
       <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -15363,15 +15908,18 @@
       <c r="U182" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V182" s="2" t="inlineStr"/>
-      <c r="W182" s="2" t="inlineStr">
+      <c r="V182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W182" s="2" t="inlineStr"/>
+      <c r="X182" s="2" t="inlineStr">
         <is>
           <t>순천만 갯벌</t>
         </is>
       </c>
-      <c r="X182" s="2" t="inlineStr"/>
       <c r="Y182" s="2" t="inlineStr"/>
       <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -15453,17 +16001,20 @@
       <c r="U183" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V183" s="2" t="inlineStr">
+      <c r="V183" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W183" s="2" t="inlineStr">
         <is>
           <t>갓김치</t>
         </is>
       </c>
-      <c r="W183" s="2" t="inlineStr"/>
-      <c r="X183" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="X183" s="2" t="inlineStr"/>
+      <c r="Y183" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -15547,17 +16098,20 @@
         <v>0</v>
       </c>
       <c r="U184" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V184" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V184" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W184" s="2" t="inlineStr">
         <is>
           <t>낙지</t>
         </is>
       </c>
-      <c r="W184" s="2" t="inlineStr"/>
       <c r="X184" s="2" t="inlineStr"/>
       <c r="Y184" s="2" t="inlineStr"/>
       <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -15637,17 +16191,20 @@
         <v>0</v>
       </c>
       <c r="U185" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V185" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V185" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W185" s="2" t="inlineStr">
         <is>
           <t>매실</t>
         </is>
       </c>
-      <c r="W185" s="2" t="inlineStr"/>
       <c r="X185" s="2" t="inlineStr"/>
       <c r="Y185" s="2" t="inlineStr"/>
       <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -15721,15 +16278,18 @@
       <c r="U186" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V186" s="2" t="inlineStr">
+      <c r="V186" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W186" s="2" t="inlineStr">
         <is>
           <t>나주 배</t>
         </is>
       </c>
-      <c r="W186" s="2" t="inlineStr"/>
       <c r="X186" s="2" t="inlineStr"/>
       <c r="Y186" s="2" t="inlineStr"/>
       <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -15815,11 +16375,14 @@
       <c r="U187" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W187" s="2" t="inlineStr"/>
       <c r="X187" s="2" t="inlineStr"/>
       <c r="Y187" s="2" t="inlineStr"/>
       <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -15901,19 +16464,22 @@
       <c r="U188" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V188" s="2" t="inlineStr">
+      <c r="V188" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W188" s="2" t="inlineStr">
         <is>
           <t>밤고구마</t>
         </is>
       </c>
-      <c r="W188" s="2" t="inlineStr"/>
       <c r="X188" s="2" t="inlineStr"/>
-      <c r="Y188" s="2" t="inlineStr">
+      <c r="Y188" s="2" t="inlineStr"/>
+      <c r="Z188" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z188" s="2" t="inlineStr"/>
+      <c r="AA188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -15983,19 +16549,22 @@
       <c r="U189" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V189" s="2" t="inlineStr"/>
-      <c r="W189" s="2" t="inlineStr">
+      <c r="V189" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W189" s="2" t="inlineStr"/>
+      <c r="X189" s="2" t="inlineStr">
         <is>
           <t>무등산 입석대</t>
         </is>
       </c>
-      <c r="X189" s="2" t="inlineStr"/>
-      <c r="Y189" s="2" t="inlineStr">
+      <c r="Y189" s="2" t="inlineStr"/>
+      <c r="Z189" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z189" s="2" t="inlineStr"/>
+      <c r="AA189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -16077,15 +16646,18 @@
       <c r="U190" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V190" s="2" t="inlineStr">
+      <c r="V190" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W190" s="2" t="inlineStr">
         <is>
           <t>유자</t>
         </is>
       </c>
-      <c r="W190" s="2" t="inlineStr"/>
       <c r="X190" s="2" t="inlineStr"/>
       <c r="Y190" s="2" t="inlineStr"/>
       <c r="Z190" s="2" t="inlineStr"/>
+      <c r="AA190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -16163,15 +16735,18 @@
       <c r="U191" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V191" s="2" t="inlineStr">
+      <c r="V191" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W191" s="2" t="inlineStr">
         <is>
           <t>굴비</t>
         </is>
       </c>
-      <c r="W191" s="2" t="inlineStr"/>
       <c r="X191" s="2" t="inlineStr"/>
       <c r="Y191" s="2" t="inlineStr"/>
-      <c r="Z191" s="2" t="inlineStr">
+      <c r="Z191" s="2" t="inlineStr"/>
+      <c r="AA191" s="2" t="inlineStr">
         <is>
           <t>2 (원자력(한빛))</t>
         </is>
@@ -16257,15 +16832,18 @@
       <c r="U192" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V192" s="2" t="inlineStr"/>
-      <c r="W192" s="2" t="inlineStr">
+      <c r="V192" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W192" s="2" t="inlineStr"/>
+      <c r="X192" s="2" t="inlineStr">
         <is>
           <t>월출산 구정봉</t>
         </is>
       </c>
-      <c r="X192" s="2" t="inlineStr"/>
       <c r="Y192" s="2" t="inlineStr"/>
       <c r="Z192" s="2" t="inlineStr"/>
+      <c r="AA192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -16351,15 +16929,18 @@
       <c r="U193" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V193" s="2" t="inlineStr">
+      <c r="V193" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W193" s="2" t="inlineStr">
         <is>
           <t>전복</t>
         </is>
       </c>
-      <c r="W193" s="2" t="inlineStr"/>
       <c r="X193" s="2" t="inlineStr"/>
       <c r="Y193" s="2" t="inlineStr"/>
       <c r="Z193" s="2" t="inlineStr"/>
+      <c r="AA193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -16433,15 +17014,18 @@
       <c r="U194" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V194" s="2" t="inlineStr">
+      <c r="V194" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W194" s="2" t="inlineStr">
         <is>
           <t>죽세공품</t>
         </is>
       </c>
-      <c r="W194" s="2" t="inlineStr"/>
       <c r="X194" s="2" t="inlineStr"/>
       <c r="Y194" s="2" t="inlineStr"/>
       <c r="Z194" s="2" t="inlineStr"/>
+      <c r="AA194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -16515,11 +17099,14 @@
       <c r="U195" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V195" s="2" t="inlineStr"/>
+      <c r="V195" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W195" s="2" t="inlineStr"/>
       <c r="X195" s="2" t="inlineStr"/>
       <c r="Y195" s="2" t="inlineStr"/>
       <c r="Z195" s="2" t="inlineStr"/>
+      <c r="AA195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -16605,19 +17192,22 @@
       <c r="U196" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V196" s="2" t="inlineStr">
+      <c r="V196" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W196" s="2" t="inlineStr">
         <is>
           <t>천일염</t>
         </is>
       </c>
-      <c r="W196" s="2" t="inlineStr">
+      <c r="X196" s="2" t="inlineStr">
         <is>
           <t>홍도</t>
         </is>
       </c>
-      <c r="X196" s="2" t="inlineStr"/>
       <c r="Y196" s="2" t="inlineStr"/>
       <c r="Z196" s="2" t="inlineStr"/>
+      <c r="AA196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -16695,19 +17285,22 @@
       <c r="U197" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V197" s="2" t="inlineStr">
+      <c r="V197" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W197" s="2" t="inlineStr">
         <is>
           <t>보성 녹차</t>
         </is>
       </c>
-      <c r="W197" s="2" t="inlineStr"/>
       <c r="X197" s="2" t="inlineStr"/>
-      <c r="Y197" s="2" t="inlineStr">
+      <c r="Y197" s="2" t="inlineStr"/>
+      <c r="Z197" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z197" s="2" t="inlineStr"/>
+      <c r="AA197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -16785,19 +17378,22 @@
       <c r="U198" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V198" s="2" t="inlineStr">
+      <c r="V198" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W198" s="2" t="inlineStr">
         <is>
           <t>표고버섯</t>
         </is>
       </c>
-      <c r="W198" s="2" t="inlineStr"/>
       <c r="X198" s="2" t="inlineStr"/>
-      <c r="Y198" s="2" t="inlineStr">
+      <c r="Y198" s="2" t="inlineStr"/>
+      <c r="Z198" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z198" s="2" t="inlineStr"/>
+      <c r="AA198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -16875,11 +17471,14 @@
       <c r="U199" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V199" s="2" t="inlineStr"/>
+      <c r="V199" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W199" s="2" t="inlineStr"/>
       <c r="X199" s="2" t="inlineStr"/>
       <c r="Y199" s="2" t="inlineStr"/>
       <c r="Z199" s="2" t="inlineStr"/>
+      <c r="AA199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -16961,11 +17560,14 @@
       <c r="U200" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V200" s="2" t="inlineStr"/>
+      <c r="V200" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W200" s="2" t="inlineStr"/>
       <c r="X200" s="2" t="inlineStr"/>
       <c r="Y200" s="2" t="inlineStr"/>
       <c r="Z200" s="2" t="inlineStr"/>
+      <c r="AA200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -17051,19 +17653,22 @@
       <c r="U201" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V201" s="2" t="inlineStr">
+      <c r="V201" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W201" s="2" t="inlineStr">
         <is>
           <t>진돗개</t>
         </is>
       </c>
-      <c r="W201" s="2" t="inlineStr">
+      <c r="X201" s="2" t="inlineStr">
         <is>
           <t>세방낙조</t>
         </is>
       </c>
-      <c r="X201" s="2" t="inlineStr"/>
       <c r="Y201" s="2" t="inlineStr"/>
       <c r="Z201" s="2" t="inlineStr"/>
+      <c r="AA201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -17137,11 +17742,14 @@
       <c r="U202" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V202" s="2" t="inlineStr"/>
+      <c r="V202" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W202" s="2" t="inlineStr"/>
       <c r="X202" s="2" t="inlineStr"/>
       <c r="Y202" s="2" t="inlineStr"/>
       <c r="Z202" s="2" t="inlineStr"/>
+      <c r="AA202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -17215,11 +17823,14 @@
       <c r="U203" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V203" s="2" t="inlineStr"/>
+      <c r="V203" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W203" s="2" t="inlineStr"/>
       <c r="X203" s="2" t="inlineStr"/>
       <c r="Y203" s="2" t="inlineStr"/>
       <c r="Z203" s="2" t="inlineStr"/>
+      <c r="AA203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -17301,19 +17912,22 @@
       <c r="U204" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V204" s="2" t="inlineStr">
+      <c r="V204" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W204" s="2" t="inlineStr">
         <is>
           <t>과메기</t>
         </is>
       </c>
-      <c r="W204" s="2" t="inlineStr">
+      <c r="X204" s="2" t="inlineStr">
         <is>
           <t>호미곶</t>
         </is>
       </c>
-      <c r="X204" s="2" t="inlineStr"/>
       <c r="Y204" s="2" t="inlineStr"/>
       <c r="Z204" s="2" t="inlineStr"/>
+      <c r="AA204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -17387,11 +18001,14 @@
       <c r="U205" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V205" s="2" t="inlineStr"/>
+      <c r="V205" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W205" s="2" t="inlineStr"/>
       <c r="X205" s="2" t="inlineStr"/>
       <c r="Y205" s="2" t="inlineStr"/>
       <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -17461,11 +18078,14 @@
       <c r="U206" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V206" s="2" t="inlineStr"/>
+      <c r="V206" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W206" s="2" t="inlineStr"/>
       <c r="X206" s="2" t="inlineStr"/>
       <c r="Y206" s="2" t="inlineStr"/>
       <c r="Z206" s="2" t="inlineStr"/>
+      <c r="AA206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -17547,15 +18167,18 @@
       <c r="U207" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V207" s="2" t="inlineStr">
+      <c r="V207" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W207" s="2" t="inlineStr">
         <is>
           <t>법주</t>
         </is>
       </c>
-      <c r="W207" s="2" t="inlineStr"/>
       <c r="X207" s="2" t="inlineStr"/>
       <c r="Y207" s="2" t="inlineStr"/>
-      <c r="Z207" s="2" t="inlineStr">
+      <c r="Z207" s="2" t="inlineStr"/>
+      <c r="AA207" s="2" t="inlineStr">
         <is>
           <t>2 (원자력(월성))</t>
         </is>
@@ -17633,15 +18256,18 @@
       <c r="U208" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V208" s="2" t="inlineStr">
+      <c r="V208" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W208" s="2" t="inlineStr">
         <is>
           <t>안동소주</t>
         </is>
       </c>
-      <c r="W208" s="2" t="inlineStr"/>
       <c r="X208" s="2" t="inlineStr"/>
       <c r="Y208" s="2" t="inlineStr"/>
-      <c r="Z208" s="2" t="inlineStr">
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr">
         <is>
           <t>1 (수력(안동댐))</t>
         </is>
@@ -17719,11 +18345,14 @@
       <c r="U209" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V209" s="2" t="inlineStr"/>
+      <c r="V209" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W209" s="2" t="inlineStr"/>
       <c r="X209" s="2" t="inlineStr"/>
       <c r="Y209" s="2" t="inlineStr"/>
       <c r="Z209" s="2" t="inlineStr"/>
+      <c r="AA209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -17797,11 +18426,14 @@
       <c r="U210" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V210" s="2" t="inlineStr"/>
+      <c r="V210" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W210" s="2" t="inlineStr"/>
       <c r="X210" s="2" t="inlineStr"/>
       <c r="Y210" s="2" t="inlineStr"/>
       <c r="Z210" s="2" t="inlineStr"/>
+      <c r="AA210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -17875,19 +18507,22 @@
       <c r="U211" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V211" s="2" t="inlineStr">
+      <c r="V211" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W211" s="2" t="inlineStr">
         <is>
           <t>영주 인삼</t>
         </is>
       </c>
-      <c r="W211" s="2" t="inlineStr">
+      <c r="X211" s="2" t="inlineStr">
         <is>
           <t>소백산 비로봉</t>
         </is>
       </c>
-      <c r="X211" s="2" t="inlineStr"/>
       <c r="Y211" s="2" t="inlineStr"/>
       <c r="Z211" s="2" t="inlineStr"/>
+      <c r="AA211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -17961,15 +18596,18 @@
       <c r="U212" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V212" s="2" t="inlineStr">
+      <c r="V212" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W212" s="2" t="inlineStr">
         <is>
           <t>영천 포도</t>
         </is>
       </c>
-      <c r="W212" s="2" t="inlineStr"/>
       <c r="X212" s="2" t="inlineStr"/>
       <c r="Y212" s="2" t="inlineStr"/>
       <c r="Z212" s="2" t="inlineStr"/>
+      <c r="AA212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -18043,15 +18681,18 @@
       <c r="U213" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V213" s="2" t="inlineStr">
+      <c r="V213" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W213" s="2" t="inlineStr">
         <is>
           <t>곶감</t>
         </is>
       </c>
-      <c r="W213" s="2" t="inlineStr"/>
       <c r="X213" s="2" t="inlineStr"/>
       <c r="Y213" s="2" t="inlineStr"/>
       <c r="Z213" s="2" t="inlineStr"/>
+      <c r="AA213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -18125,15 +18766,18 @@
       <c r="U214" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V214" s="2" t="inlineStr"/>
+      <c r="V214" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W214" s="2" t="inlineStr"/>
       <c r="X214" s="2" t="inlineStr"/>
-      <c r="Y214" s="2" t="inlineStr">
+      <c r="Y214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="AA214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -18207,15 +18851,18 @@
       <c r="U215" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V215" s="2" t="inlineStr"/>
-      <c r="W215" s="2" t="inlineStr">
+      <c r="V215" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W215" s="2" t="inlineStr"/>
+      <c r="X215" s="2" t="inlineStr">
         <is>
           <t>회룡포</t>
         </is>
       </c>
-      <c r="X215" s="2" t="inlineStr"/>
       <c r="Y215" s="2" t="inlineStr"/>
       <c r="Z215" s="2" t="inlineStr"/>
+      <c r="AA215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -18289,15 +18936,18 @@
       <c r="U216" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V216" s="2" t="inlineStr">
+      <c r="V216" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W216" s="2" t="inlineStr">
         <is>
           <t>의성 마늘</t>
         </is>
       </c>
-      <c r="W216" s="2" t="inlineStr"/>
       <c r="X216" s="2" t="inlineStr"/>
       <c r="Y216" s="2" t="inlineStr"/>
       <c r="Z216" s="2" t="inlineStr"/>
+      <c r="AA216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -18379,11 +19029,14 @@
       <c r="U217" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V217" s="2" t="inlineStr"/>
+      <c r="V217" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W217" s="2" t="inlineStr"/>
       <c r="X217" s="2" t="inlineStr"/>
       <c r="Y217" s="2" t="inlineStr"/>
-      <c r="Z217" s="2" t="inlineStr">
+      <c r="Z217" s="2" t="inlineStr"/>
+      <c r="AA217" s="2" t="inlineStr">
         <is>
           <t>2 (원자력(한울))</t>
         </is>
@@ -18461,15 +19114,18 @@
       <c r="U218" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V218" s="2" t="inlineStr">
+      <c r="V218" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W218" s="2" t="inlineStr">
         <is>
           <t>참외</t>
         </is>
       </c>
-      <c r="W218" s="2" t="inlineStr"/>
       <c r="X218" s="2" t="inlineStr"/>
       <c r="Y218" s="2" t="inlineStr"/>
       <c r="Z218" s="2" t="inlineStr"/>
+      <c r="AA218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -18543,15 +19199,18 @@
       <c r="U219" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V219" s="2" t="inlineStr">
+      <c r="V219" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W219" s="2" t="inlineStr">
         <is>
           <t>반시</t>
         </is>
       </c>
-      <c r="W219" s="2" t="inlineStr"/>
       <c r="X219" s="2" t="inlineStr"/>
       <c r="Y219" s="2" t="inlineStr"/>
       <c r="Z219" s="2" t="inlineStr"/>
+      <c r="AA219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -18633,19 +19292,22 @@
       <c r="U220" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V220" s="2" t="inlineStr">
+      <c r="V220" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W220" s="2" t="inlineStr">
         <is>
           <t>대게</t>
         </is>
       </c>
-      <c r="W220" s="2" t="inlineStr">
+      <c r="X220" s="2" t="inlineStr">
         <is>
           <t>고래불해변</t>
         </is>
       </c>
-      <c r="X220" s="2" t="inlineStr"/>
       <c r="Y220" s="2" t="inlineStr"/>
       <c r="Z220" s="2" t="inlineStr"/>
+      <c r="AA220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -18719,15 +19381,18 @@
       <c r="U221" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V221" s="2" t="inlineStr">
+      <c r="V221" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W221" s="2" t="inlineStr">
         <is>
           <t>고령 수박</t>
         </is>
       </c>
-      <c r="W221" s="2" t="inlineStr"/>
       <c r="X221" s="2" t="inlineStr"/>
       <c r="Y221" s="2" t="inlineStr"/>
       <c r="Z221" s="2" t="inlineStr"/>
+      <c r="AA221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -18801,15 +19466,18 @@
       <c r="U222" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V222" s="2" t="inlineStr">
+      <c r="V222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W222" s="2" t="inlineStr">
         <is>
           <t>봉화 송이</t>
         </is>
       </c>
-      <c r="W222" s="2" t="inlineStr"/>
       <c r="X222" s="2" t="inlineStr"/>
       <c r="Y222" s="2" t="inlineStr"/>
       <c r="Z222" s="2" t="inlineStr"/>
+      <c r="AA222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -18883,19 +19551,22 @@
       <c r="U223" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V223" s="2" t="inlineStr">
+      <c r="V223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W223" s="2" t="inlineStr">
         <is>
           <t>청송 사과</t>
         </is>
       </c>
-      <c r="W223" s="2" t="inlineStr">
+      <c r="X223" s="2" t="inlineStr">
         <is>
           <t>주왕산 용연폭포</t>
         </is>
       </c>
-      <c r="X223" s="2" t="inlineStr"/>
       <c r="Y223" s="2" t="inlineStr"/>
       <c r="Z223" s="2" t="inlineStr"/>
+      <c r="AA223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -18969,15 +19640,18 @@
       <c r="U224" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V224" s="2" t="inlineStr">
+      <c r="V224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W224" s="2" t="inlineStr">
         <is>
           <t>청양고추</t>
         </is>
       </c>
-      <c r="W224" s="2" t="inlineStr"/>
       <c r="X224" s="2" t="inlineStr"/>
       <c r="Y224" s="2" t="inlineStr"/>
       <c r="Z224" s="2" t="inlineStr"/>
+      <c r="AA224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -19055,19 +19729,22 @@
       <c r="U225" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V225" s="2" t="inlineStr">
+      <c r="V225" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W225" s="2" t="inlineStr">
         <is>
           <t>독도새우, 명이</t>
         </is>
       </c>
-      <c r="W225" s="2" t="inlineStr">
+      <c r="X225" s="2" t="inlineStr">
         <is>
           <t>나리분지</t>
         </is>
       </c>
-      <c r="X225" s="2" t="inlineStr"/>
       <c r="Y225" s="2" t="inlineStr"/>
       <c r="Z225" s="2" t="inlineStr"/>
+      <c r="AA225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -19149,11 +19826,14 @@
       <c r="U226" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V226" s="2" t="inlineStr"/>
+      <c r="V226" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W226" s="2" t="inlineStr"/>
       <c r="X226" s="2" t="inlineStr"/>
       <c r="Y226" s="2" t="inlineStr"/>
       <c r="Z226" s="2" t="inlineStr"/>
+      <c r="AA226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -19227,11 +19907,14 @@
       <c r="U227" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V227" s="2" t="inlineStr"/>
+      <c r="V227" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W227" s="2" t="inlineStr"/>
       <c r="X227" s="2" t="inlineStr"/>
       <c r="Y227" s="2" t="inlineStr"/>
       <c r="Z227" s="2" t="inlineStr"/>
+      <c r="AA227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -19305,11 +19988,14 @@
       <c r="U228" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W228" s="2" t="inlineStr"/>
       <c r="X228" s="2" t="inlineStr"/>
       <c r="Y228" s="2" t="inlineStr"/>
       <c r="Z228" s="2" t="inlineStr"/>
+      <c r="AA228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -19379,15 +20065,18 @@
       <c r="U229" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V229" s="2" t="inlineStr">
+      <c r="V229" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W229" s="2" t="inlineStr">
         <is>
           <t>냉면</t>
         </is>
       </c>
-      <c r="W229" s="2" t="inlineStr"/>
       <c r="X229" s="2" t="inlineStr"/>
       <c r="Y229" s="2" t="inlineStr"/>
       <c r="Z229" s="2" t="inlineStr"/>
+      <c r="AA229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -19473,15 +20162,18 @@
       <c r="U230" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V230" s="2" t="inlineStr"/>
-      <c r="W230" s="2" t="inlineStr">
+      <c r="V230" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W230" s="2" t="inlineStr"/>
+      <c r="X230" s="2" t="inlineStr">
         <is>
           <t>해금강</t>
         </is>
       </c>
-      <c r="X230" s="2" t="inlineStr"/>
       <c r="Y230" s="2" t="inlineStr"/>
       <c r="Z230" s="2" t="inlineStr"/>
+      <c r="AA230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -19563,19 +20255,22 @@
       <c r="U231" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V231" s="2" t="inlineStr">
+      <c r="V231" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W231" s="2" t="inlineStr">
         <is>
           <t>통영 굴</t>
         </is>
       </c>
-      <c r="W231" s="2" t="inlineStr">
+      <c r="X231" s="2" t="inlineStr">
         <is>
           <t>한려해상</t>
         </is>
       </c>
-      <c r="X231" s="2" t="inlineStr"/>
       <c r="Y231" s="2" t="inlineStr"/>
       <c r="Z231" s="2" t="inlineStr"/>
+      <c r="AA231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -19657,15 +20352,18 @@
       <c r="U232" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V232" s="2" t="inlineStr">
+      <c r="V232" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W232" s="2" t="inlineStr">
         <is>
           <t>쥐치포</t>
         </is>
       </c>
-      <c r="W232" s="2" t="inlineStr"/>
       <c r="X232" s="2" t="inlineStr"/>
       <c r="Y232" s="2" t="inlineStr"/>
       <c r="Z232" s="2" t="inlineStr"/>
+      <c r="AA232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -19739,19 +20437,22 @@
       <c r="U233" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V233" s="2" t="inlineStr">
+      <c r="V233" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W233" s="2" t="inlineStr">
         <is>
           <t>얼음골사과</t>
         </is>
       </c>
-      <c r="W233" s="2" t="inlineStr">
+      <c r="X233" s="2" t="inlineStr">
         <is>
           <t>얼음골</t>
         </is>
       </c>
-      <c r="X233" s="2" t="inlineStr"/>
       <c r="Y233" s="2" t="inlineStr"/>
       <c r="Z233" s="2" t="inlineStr"/>
+      <c r="AA233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -19825,11 +20526,14 @@
       <c r="U234" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V234" s="2" t="inlineStr"/>
+      <c r="V234" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W234" s="2" t="inlineStr"/>
       <c r="X234" s="2" t="inlineStr"/>
       <c r="Y234" s="2" t="inlineStr"/>
       <c r="Z234" s="2" t="inlineStr"/>
+      <c r="AA234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -19903,15 +20607,18 @@
       <c r="U235" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V235" s="2" t="inlineStr">
+      <c r="V235" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W235" s="2" t="inlineStr">
         <is>
           <t>함안 수박</t>
         </is>
       </c>
-      <c r="W235" s="2" t="inlineStr"/>
       <c r="X235" s="2" t="inlineStr"/>
       <c r="Y235" s="2" t="inlineStr"/>
       <c r="Z235" s="2" t="inlineStr"/>
+      <c r="AA235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -19985,15 +20692,18 @@
       <c r="U236" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V236" s="2" t="inlineStr"/>
-      <c r="W236" s="2" t="inlineStr">
+      <c r="V236" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W236" s="2" t="inlineStr"/>
+      <c r="X236" s="2" t="inlineStr">
         <is>
           <t>우포늪</t>
         </is>
       </c>
-      <c r="X236" s="2" t="inlineStr"/>
       <c r="Y236" s="2" t="inlineStr"/>
       <c r="Z236" s="2" t="inlineStr"/>
+      <c r="AA236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -20071,11 +20781,14 @@
       <c r="U237" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V237" s="2" t="inlineStr"/>
+      <c r="V237" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W237" s="2" t="inlineStr"/>
       <c r="X237" s="2" t="inlineStr"/>
       <c r="Y237" s="2" t="inlineStr"/>
       <c r="Z237" s="2" t="inlineStr"/>
+      <c r="AA237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -20161,15 +20874,18 @@
       <c r="U238" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V238" s="2" t="inlineStr">
+      <c r="V238" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W238" s="2" t="inlineStr">
         <is>
           <t>죽방멸치</t>
         </is>
       </c>
-      <c r="W238" s="2" t="inlineStr"/>
       <c r="X238" s="2" t="inlineStr"/>
       <c r="Y238" s="2" t="inlineStr"/>
       <c r="Z238" s="2" t="inlineStr"/>
+      <c r="AA238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -20255,15 +20971,18 @@
       <c r="U239" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V239" s="2" t="inlineStr">
+      <c r="V239" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W239" s="2" t="inlineStr">
         <is>
           <t>하동 녹차</t>
         </is>
       </c>
-      <c r="W239" s="2" t="inlineStr"/>
       <c r="X239" s="2" t="inlineStr"/>
       <c r="Y239" s="2" t="inlineStr"/>
       <c r="Z239" s="2" t="inlineStr"/>
+      <c r="AA239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -20337,11 +21056,14 @@
       <c r="U240" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V240" s="2" t="inlineStr"/>
+      <c r="V240" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W240" s="2" t="inlineStr"/>
       <c r="X240" s="2" t="inlineStr"/>
       <c r="Y240" s="2" t="inlineStr"/>
-      <c r="Z240" s="2" t="inlineStr">
+      <c r="Z240" s="2" t="inlineStr"/>
+      <c r="AA240" s="2" t="inlineStr">
         <is>
           <t>1 (수력(합천댐))</t>
         </is>
@@ -20419,11 +21141,14 @@
       <c r="U241" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V241" s="2" t="inlineStr"/>
+      <c r="V241" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W241" s="2" t="inlineStr"/>
       <c r="X241" s="2" t="inlineStr"/>
       <c r="Y241" s="2" t="inlineStr"/>
       <c r="Z241" s="2" t="inlineStr"/>
+      <c r="AA241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -20493,15 +21218,18 @@
       <c r="U242" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V242" s="2" t="inlineStr"/>
-      <c r="W242" s="2" t="inlineStr">
+      <c r="V242" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W242" s="2" t="inlineStr"/>
+      <c r="X242" s="2" t="inlineStr">
         <is>
           <t>지리산 천왕봉</t>
         </is>
       </c>
-      <c r="X242" s="2" t="inlineStr"/>
       <c r="Y242" s="2" t="inlineStr"/>
       <c r="Z242" s="2" t="inlineStr"/>
+      <c r="AA242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -20575,15 +21303,18 @@
       <c r="U243" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V243" s="2" t="inlineStr">
+      <c r="V243" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W243" s="2" t="inlineStr">
         <is>
           <t>망개떡</t>
         </is>
       </c>
-      <c r="W243" s="2" t="inlineStr"/>
       <c r="X243" s="2" t="inlineStr"/>
       <c r="Y243" s="2" t="inlineStr"/>
       <c r="Z243" s="2" t="inlineStr"/>
+      <c r="AA243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -20665,19 +21396,22 @@
       <c r="U244" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V244" s="2" t="inlineStr">
+      <c r="V244" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W244" s="2" t="inlineStr">
         <is>
           <t>흑돼지, 감귤</t>
         </is>
       </c>
-      <c r="W244" s="2" t="inlineStr">
+      <c r="X244" s="2" t="inlineStr">
         <is>
           <t>한라산 백록담</t>
         </is>
       </c>
-      <c r="X244" s="2" t="inlineStr"/>
       <c r="Y244" s="2" t="inlineStr"/>
       <c r="Z244" s="2" t="inlineStr"/>
+      <c r="AA244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -20759,19 +21493,22 @@
       <c r="U245" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V245" s="2" t="inlineStr">
+      <c r="V245" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W245" s="2" t="inlineStr">
         <is>
           <t>한라봉, 은갈치</t>
         </is>
       </c>
-      <c r="W245" s="2" t="inlineStr">
+      <c r="X245" s="2" t="inlineStr">
         <is>
           <t>성산일출봉</t>
         </is>
       </c>
-      <c r="X245" s="2" t="inlineStr"/>
       <c r="Y245" s="2" t="inlineStr"/>
       <c r="Z245" s="2" t="inlineStr"/>
+      <c r="AA245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -20857,19 +21594,22 @@
       <c r="U246" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V246" s="2" t="inlineStr">
+      <c r="V246" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W246" s="2" t="inlineStr">
         <is>
           <t>꽃게</t>
         </is>
       </c>
-      <c r="W246" s="2" t="inlineStr">
+      <c r="X246" s="2" t="inlineStr">
         <is>
           <t>두무진</t>
         </is>
       </c>
-      <c r="X246" s="2" t="n"/>
       <c r="Y246" s="2" t="n"/>
       <c r="Z246" s="2" t="n"/>
+      <c r="AA246" s="2" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -20943,11 +21683,14 @@
       <c r="U247" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V247" s="2" t="inlineStr"/>
+      <c r="V247" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W247" s="2" t="inlineStr"/>
       <c r="X247" s="2" t="inlineStr"/>
       <c r="Y247" s="2" t="inlineStr"/>
       <c r="Z247" s="2" t="inlineStr"/>
+      <c r="AA247" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -21021,11 +21764,14 @@
       <c r="U248" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V248" s="2" t="inlineStr"/>
+      <c r="V248" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W248" s="2" t="inlineStr"/>
       <c r="X248" s="2" t="inlineStr"/>
       <c r="Y248" s="2" t="inlineStr"/>
       <c r="Z248" s="2" t="inlineStr"/>
+      <c r="AA248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -21099,15 +21845,18 @@
       <c r="U249" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V249" s="2" t="inlineStr"/>
+      <c r="V249" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W249" s="2" t="inlineStr"/>
       <c r="X249" s="2" t="inlineStr"/>
-      <c r="Y249" s="2" t="inlineStr">
+      <c r="Y249" s="2" t="inlineStr"/>
+      <c r="Z249" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z249" s="2" t="inlineStr"/>
+      <c r="AA249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -21181,15 +21930,18 @@
       <c r="U250" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V250" s="2" t="inlineStr">
+      <c r="V250" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W250" s="2" t="inlineStr">
         <is>
           <t>숭어</t>
         </is>
       </c>
-      <c r="W250" s="2" t="inlineStr"/>
       <c r="X250" s="2" t="inlineStr"/>
       <c r="Y250" s="2" t="inlineStr"/>
       <c r="Z250" s="2" t="inlineStr"/>
+      <c r="AA250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -21263,11 +22015,14 @@
       <c r="U251" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V251" s="2" t="inlineStr"/>
+      <c r="V251" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W251" s="2" t="inlineStr"/>
       <c r="X251" s="2" t="inlineStr"/>
       <c r="Y251" s="2" t="inlineStr"/>
       <c r="Z251" s="2" t="inlineStr"/>
+      <c r="AA251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -21341,11 +22096,14 @@
       <c r="U252" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V252" s="2" t="inlineStr"/>
+      <c r="V252" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W252" s="2" t="inlineStr"/>
       <c r="X252" s="2" t="inlineStr"/>
       <c r="Y252" s="2" t="inlineStr"/>
       <c r="Z252" s="2" t="inlineStr"/>
+      <c r="AA252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -21415,11 +22173,14 @@
       <c r="U253" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V253" s="2" t="inlineStr"/>
+      <c r="V253" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W253" s="2" t="inlineStr"/>
       <c r="X253" s="2" t="inlineStr"/>
       <c r="Y253" s="2" t="inlineStr"/>
       <c r="Z253" s="2" t="inlineStr"/>
+      <c r="AA253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -21493,11 +22254,14 @@
       <c r="U254" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V254" s="2" t="inlineStr"/>
+      <c r="V254" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W254" s="2" t="inlineStr"/>
       <c r="X254" s="2" t="inlineStr"/>
       <c r="Y254" s="2" t="inlineStr"/>
       <c r="Z254" s="2" t="inlineStr"/>
+      <c r="AA254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -21567,11 +22331,14 @@
       <c r="U255" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V255" s="2" t="inlineStr"/>
+      <c r="V255" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W255" s="2" t="inlineStr"/>
       <c r="X255" s="2" t="inlineStr"/>
       <c r="Y255" s="2" t="inlineStr"/>
       <c r="Z255" s="2" t="inlineStr"/>
+      <c r="AA255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -21645,11 +22412,14 @@
       <c r="U256" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V256" s="2" t="inlineStr"/>
+      <c r="V256" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W256" s="2" t="inlineStr"/>
       <c r="X256" s="2" t="inlineStr"/>
       <c r="Y256" s="2" t="inlineStr"/>
       <c r="Z256" s="2" t="inlineStr"/>
+      <c r="AA256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -21723,15 +22493,18 @@
       <c r="U257" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V257" s="2" t="inlineStr"/>
-      <c r="W257" s="2" t="inlineStr">
+      <c r="V257" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W257" s="2" t="inlineStr"/>
+      <c r="X257" s="2" t="inlineStr">
         <is>
           <t>금수산 모란봉</t>
         </is>
       </c>
-      <c r="X257" s="2" t="inlineStr"/>
       <c r="Y257" s="2" t="inlineStr"/>
       <c r="Z257" s="2" t="inlineStr"/>
+      <c r="AA257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -21801,11 +22574,14 @@
       <c r="U258" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V258" s="2" t="inlineStr"/>
+      <c r="V258" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W258" s="2" t="inlineStr"/>
       <c r="X258" s="2" t="inlineStr"/>
       <c r="Y258" s="2" t="inlineStr"/>
       <c r="Z258" s="2" t="inlineStr"/>
+      <c r="AA258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -21879,19 +22655,22 @@
       <c r="U259" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V259" s="2" t="inlineStr">
+      <c r="V259" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W259" s="2" t="inlineStr">
         <is>
           <t>평양냉면</t>
         </is>
       </c>
-      <c r="W259" s="2" t="inlineStr">
+      <c r="X259" s="2" t="inlineStr">
         <is>
           <t>능라도</t>
         </is>
       </c>
-      <c r="X259" s="2" t="inlineStr"/>
       <c r="Y259" s="2" t="inlineStr"/>
       <c r="Z259" s="2" t="inlineStr"/>
+      <c r="AA259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -21965,15 +22744,18 @@
       <c r="U260" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V260" s="2" t="inlineStr">
+      <c r="V260" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W260" s="2" t="inlineStr">
         <is>
           <t>대성 밤</t>
         </is>
       </c>
-      <c r="W260" s="2" t="inlineStr"/>
       <c r="X260" s="2" t="inlineStr"/>
       <c r="Y260" s="2" t="inlineStr"/>
       <c r="Z260" s="2" t="inlineStr"/>
+      <c r="AA260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -22043,11 +22825,14 @@
       <c r="U261" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V261" s="2" t="inlineStr"/>
+      <c r="V261" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W261" s="2" t="inlineStr"/>
       <c r="X261" s="2" t="inlineStr"/>
       <c r="Y261" s="2" t="inlineStr"/>
       <c r="Z261" s="2" t="inlineStr"/>
+      <c r="AA261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -22117,11 +22902,14 @@
       <c r="U262" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V262" s="2" t="inlineStr"/>
+      <c r="V262" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W262" s="2" t="inlineStr"/>
       <c r="X262" s="2" t="inlineStr"/>
       <c r="Y262" s="2" t="inlineStr"/>
       <c r="Z262" s="2" t="inlineStr"/>
+      <c r="AA262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -22191,11 +22979,14 @@
       <c r="U263" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V263" s="2" t="inlineStr"/>
+      <c r="V263" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W263" s="2" t="inlineStr"/>
       <c r="X263" s="2" t="inlineStr"/>
       <c r="Y263" s="2" t="inlineStr"/>
       <c r="Z263" s="2" t="inlineStr"/>
+      <c r="AA263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -22269,11 +23060,14 @@
       <c r="U264" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V264" s="2" t="inlineStr"/>
+      <c r="V264" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W264" s="2" t="inlineStr"/>
       <c r="X264" s="2" t="inlineStr"/>
       <c r="Y264" s="2" t="inlineStr"/>
       <c r="Z264" s="2" t="inlineStr"/>
+      <c r="AA264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -22347,11 +23141,14 @@
       <c r="U265" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V265" s="2" t="inlineStr"/>
+      <c r="V265" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W265" s="2" t="inlineStr"/>
       <c r="X265" s="2" t="inlineStr"/>
       <c r="Y265" s="2" t="inlineStr"/>
       <c r="Z265" s="2" t="inlineStr"/>
+      <c r="AA265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -22421,11 +23218,14 @@
       <c r="U266" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V266" s="2" t="inlineStr"/>
+      <c r="V266" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W266" s="2" t="inlineStr"/>
       <c r="X266" s="2" t="inlineStr"/>
       <c r="Y266" s="2" t="inlineStr"/>
       <c r="Z266" s="2" t="inlineStr"/>
+      <c r="AA266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -22505,17 +23305,20 @@
         <v>0</v>
       </c>
       <c r="U267" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V267" s="2" t="inlineStr"/>
-      <c r="W267" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V267" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W267" s="2" t="inlineStr"/>
+      <c r="X267" s="2" t="inlineStr">
         <is>
           <t>대동강 하구</t>
         </is>
       </c>
-      <c r="X267" s="2" t="inlineStr"/>
       <c r="Y267" s="2" t="inlineStr"/>
       <c r="Z267" s="2" t="inlineStr"/>
+      <c r="AA267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -22589,19 +23392,22 @@
       <c r="U268" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V268" s="2" t="inlineStr">
+      <c r="V268" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W268" s="2" t="inlineStr">
         <is>
           <t>강서약수</t>
         </is>
       </c>
-      <c r="W268" s="2" t="inlineStr"/>
       <c r="X268" s="2" t="inlineStr"/>
-      <c r="Y268" s="2" t="inlineStr">
+      <c r="Y268" s="2" t="inlineStr"/>
+      <c r="Z268" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z268" s="2" t="inlineStr"/>
+      <c r="AA268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -22683,15 +23489,18 @@
       <c r="U269" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V269" s="2" t="inlineStr">
+      <c r="V269" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W269" s="2" t="inlineStr">
         <is>
           <t>온천 소금</t>
         </is>
       </c>
-      <c r="W269" s="2" t="inlineStr"/>
       <c r="X269" s="2" t="inlineStr"/>
       <c r="Y269" s="2" t="inlineStr"/>
       <c r="Z269" s="2" t="inlineStr"/>
+      <c r="AA269" s="2" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -22765,11 +23574,14 @@
       <c r="U270" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V270" s="2" t="inlineStr"/>
+      <c r="V270" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W270" s="2" t="inlineStr"/>
       <c r="X270" s="2" t="inlineStr"/>
       <c r="Y270" s="2" t="inlineStr"/>
       <c r="Z270" s="2" t="inlineStr"/>
+      <c r="AA270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -22851,11 +23663,14 @@
       <c r="U271" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V271" s="2" t="inlineStr"/>
+      <c r="V271" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W271" s="2" t="inlineStr"/>
       <c r="X271" s="2" t="inlineStr"/>
       <c r="Y271" s="2" t="inlineStr"/>
       <c r="Z271" s="2" t="inlineStr"/>
+      <c r="AA271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -22937,15 +23752,18 @@
       <c r="U272" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V272" s="2" t="inlineStr">
+      <c r="V272" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W272" s="2" t="inlineStr">
         <is>
           <t>흰복숭아</t>
         </is>
       </c>
-      <c r="W272" s="2" t="inlineStr"/>
       <c r="X272" s="2" t="inlineStr"/>
       <c r="Y272" s="2" t="inlineStr"/>
       <c r="Z272" s="2" t="inlineStr"/>
+      <c r="AA272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -23021,17 +23839,20 @@
         <v>0</v>
       </c>
       <c r="U273" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V273" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V273" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W273" s="2" t="inlineStr">
         <is>
           <t>해삼</t>
         </is>
       </c>
-      <c r="W273" s="2" t="inlineStr"/>
       <c r="X273" s="2" t="inlineStr"/>
       <c r="Y273" s="2" t="inlineStr"/>
       <c r="Z273" s="2" t="inlineStr"/>
+      <c r="AA273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -23109,21 +23930,24 @@
       <c r="U274" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V274" s="2" t="inlineStr">
+      <c r="V274" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W274" s="2" t="inlineStr">
         <is>
           <t>선봉 굴</t>
         </is>
       </c>
-      <c r="W274" s="2" t="inlineStr">
+      <c r="X274" s="2" t="inlineStr">
         <is>
           <t>두만강 하구</t>
         </is>
       </c>
-      <c r="X274" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y274" s="2" t="inlineStr"/>
+      <c r="Y274" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Z274" s="2" t="inlineStr"/>
+      <c r="AA274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -23209,11 +24033,14 @@
       <c r="U275" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V275" s="2" t="inlineStr"/>
+      <c r="V275" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W275" s="2" t="inlineStr"/>
       <c r="X275" s="2" t="inlineStr"/>
       <c r="Y275" s="2" t="inlineStr"/>
       <c r="Z275" s="2" t="inlineStr"/>
+      <c r="AA275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -23283,15 +24110,18 @@
       <c r="U276" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V276" s="2" t="inlineStr">
+      <c r="V276" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W276" s="2" t="inlineStr">
         <is>
           <t>구성 배</t>
         </is>
       </c>
-      <c r="W276" s="2" t="inlineStr"/>
       <c r="X276" s="2" t="inlineStr"/>
       <c r="Y276" s="2" t="inlineStr"/>
       <c r="Z276" s="2" t="inlineStr"/>
+      <c r="AA276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -23369,15 +24199,18 @@
       <c r="U277" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V277" s="2" t="inlineStr">
+      <c r="V277" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W277" s="2" t="inlineStr">
         <is>
           <t>왕밤</t>
         </is>
       </c>
-      <c r="W277" s="2" t="inlineStr"/>
       <c r="X277" s="2" t="inlineStr"/>
       <c r="Y277" s="2" t="inlineStr"/>
       <c r="Z277" s="2" t="inlineStr"/>
+      <c r="AA277" s="2" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -23447,19 +24280,22 @@
       <c r="U278" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V278" s="2" t="inlineStr">
+      <c r="V278" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W278" s="2" t="inlineStr">
         <is>
           <t>빙어</t>
         </is>
       </c>
-      <c r="W278" s="2" t="inlineStr">
+      <c r="X278" s="2" t="inlineStr">
         <is>
           <t>수풍호</t>
         </is>
       </c>
-      <c r="X278" s="2" t="inlineStr"/>
       <c r="Y278" s="2" t="inlineStr"/>
-      <c r="Z278" s="2" t="inlineStr">
+      <c r="Z278" s="2" t="inlineStr"/>
+      <c r="AA278" s="2" t="inlineStr">
         <is>
           <t>1 (수력(수풍))</t>
         </is>
@@ -23537,23 +24373,26 @@
       <c r="U279" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V279" s="2" t="inlineStr">
+      <c r="V279" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W279" s="2" t="inlineStr">
         <is>
           <t>칠색송어</t>
         </is>
       </c>
-      <c r="W279" s="2" t="inlineStr">
+      <c r="X279" s="2" t="inlineStr">
         <is>
           <t>용문대굴</t>
         </is>
       </c>
-      <c r="X279" s="2" t="inlineStr"/>
-      <c r="Y279" s="2" t="inlineStr">
+      <c r="Y279" s="2" t="inlineStr"/>
+      <c r="Z279" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z279" s="2" t="inlineStr"/>
+      <c r="AA279" s="2" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -23631,11 +24470,14 @@
       <c r="U280" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V280" s="2" t="inlineStr"/>
+      <c r="V280" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W280" s="2" t="inlineStr"/>
       <c r="X280" s="2" t="inlineStr"/>
       <c r="Y280" s="2" t="inlineStr"/>
       <c r="Z280" s="2" t="inlineStr"/>
+      <c r="AA280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -23713,11 +24555,14 @@
       <c r="U281" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V281" s="2" t="inlineStr"/>
+      <c r="V281" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W281" s="2" t="inlineStr"/>
       <c r="X281" s="2" t="inlineStr"/>
       <c r="Y281" s="2" t="inlineStr"/>
       <c r="Z281" s="2" t="inlineStr"/>
+      <c r="AA281" s="2" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -23791,23 +24636,26 @@
       <c r="U282" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V282" s="2" t="inlineStr">
+      <c r="V282" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W282" s="2" t="inlineStr">
         <is>
           <t>비단</t>
         </is>
       </c>
-      <c r="W282" s="2" t="inlineStr">
+      <c r="X282" s="2" t="inlineStr">
         <is>
           <t>약산동대</t>
         </is>
       </c>
-      <c r="X282" s="2" t="inlineStr"/>
-      <c r="Y282" s="2" t="inlineStr">
+      <c r="Y282" s="2" t="inlineStr"/>
+      <c r="Z282" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z282" s="2" t="inlineStr"/>
+      <c r="AA282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -23885,11 +24733,14 @@
       <c r="U283" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V283" s="2" t="inlineStr"/>
+      <c r="V283" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W283" s="2" t="inlineStr"/>
       <c r="X283" s="2" t="inlineStr"/>
       <c r="Y283" s="2" t="inlineStr"/>
       <c r="Z283" s="2" t="inlineStr"/>
+      <c r="AA283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -23959,13 +24810,16 @@
       <c r="U284" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V284" s="2" t="inlineStr"/>
+      <c r="V284" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W284" s="2" t="inlineStr"/>
-      <c r="X284" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y284" s="2" t="inlineStr"/>
+      <c r="X284" s="2" t="inlineStr"/>
+      <c r="Y284" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="Z284" s="2" t="inlineStr"/>
+      <c r="AA284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -24035,15 +24889,18 @@
       <c r="U285" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V285" s="2" t="inlineStr">
+      <c r="V285" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W285" s="2" t="inlineStr">
         <is>
           <t>의주 쌀</t>
         </is>
       </c>
-      <c r="W285" s="2" t="inlineStr"/>
       <c r="X285" s="2" t="inlineStr"/>
       <c r="Y285" s="2" t="inlineStr"/>
       <c r="Z285" s="2" t="inlineStr"/>
+      <c r="AA285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -24113,15 +24970,18 @@
       <c r="U286" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V286" s="2" t="inlineStr">
+      <c r="V286" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W286" s="2" t="inlineStr">
         <is>
           <t>옻</t>
         </is>
       </c>
-      <c r="W286" s="2" t="inlineStr"/>
       <c r="X286" s="2" t="inlineStr"/>
       <c r="Y286" s="2" t="inlineStr"/>
-      <c r="Z286" s="2" t="inlineStr">
+      <c r="Z286" s="2" t="inlineStr"/>
+      <c r="AA286" s="2" t="inlineStr">
         <is>
           <t>1 (수력(태천))</t>
         </is>
@@ -24195,15 +25055,18 @@
       <c r="U287" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V287" s="2" t="inlineStr"/>
-      <c r="W287" s="2" t="inlineStr">
+      <c r="V287" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W287" s="2" t="inlineStr"/>
+      <c r="X287" s="2" t="inlineStr">
         <is>
           <t>동림폭포</t>
         </is>
       </c>
-      <c r="X287" s="2" t="inlineStr"/>
       <c r="Y287" s="2" t="inlineStr"/>
       <c r="Z287" s="2" t="inlineStr"/>
+      <c r="AA287" s="2" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -24277,15 +25140,18 @@
       <c r="U288" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V288" s="2" t="inlineStr">
+      <c r="V288" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W288" s="2" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="W288" s="2" t="inlineStr"/>
       <c r="X288" s="2" t="inlineStr"/>
       <c r="Y288" s="2" t="inlineStr"/>
       <c r="Z288" s="2" t="inlineStr"/>
+      <c r="AA288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -24363,11 +25229,14 @@
       <c r="U289" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V289" s="2" t="inlineStr"/>
+      <c r="V289" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W289" s="2" t="inlineStr"/>
       <c r="X289" s="2" t="inlineStr"/>
       <c r="Y289" s="2" t="inlineStr"/>
       <c r="Z289" s="2" t="inlineStr"/>
+      <c r="AA289" s="2" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -24441,11 +25310,14 @@
       <c r="U290" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V290" s="2" t="inlineStr"/>
+      <c r="V290" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W290" s="2" t="inlineStr"/>
       <c r="X290" s="2" t="inlineStr"/>
       <c r="Y290" s="2" t="inlineStr"/>
       <c r="Z290" s="2" t="inlineStr"/>
+      <c r="AA290" s="2" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -24523,11 +25395,14 @@
       <c r="U291" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V291" s="2" t="inlineStr"/>
+      <c r="V291" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W291" s="2" t="inlineStr"/>
       <c r="X291" s="2" t="inlineStr"/>
       <c r="Y291" s="2" t="inlineStr"/>
       <c r="Z291" s="2" t="inlineStr"/>
+      <c r="AA291" s="2" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -24605,11 +25480,14 @@
       <c r="U292" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V292" s="2" t="inlineStr"/>
+      <c r="V292" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W292" s="2" t="inlineStr"/>
       <c r="X292" s="2" t="inlineStr"/>
       <c r="Y292" s="2" t="inlineStr"/>
       <c r="Z292" s="2" t="inlineStr"/>
+      <c r="AA292" s="2" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -24679,11 +25557,14 @@
       <c r="U293" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V293" s="2" t="inlineStr"/>
+      <c r="V293" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W293" s="2" t="inlineStr"/>
       <c r="X293" s="2" t="inlineStr"/>
       <c r="Y293" s="2" t="inlineStr"/>
       <c r="Z293" s="2" t="inlineStr"/>
+      <c r="AA293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -24757,15 +25638,18 @@
       <c r="U294" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V294" s="2" t="inlineStr"/>
-      <c r="W294" s="2" t="inlineStr">
+      <c r="V294" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W294" s="2" t="inlineStr"/>
+      <c r="X294" s="2" t="inlineStr">
         <is>
           <t>묘향산 비로봉</t>
         </is>
       </c>
-      <c r="X294" s="2" t="inlineStr"/>
       <c r="Y294" s="2" t="inlineStr"/>
       <c r="Z294" s="2" t="inlineStr"/>
+      <c r="AA294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -24835,11 +25719,14 @@
       <c r="U295" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V295" s="2" t="inlineStr"/>
+      <c r="V295" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W295" s="2" t="inlineStr"/>
       <c r="X295" s="2" t="inlineStr"/>
       <c r="Y295" s="2" t="inlineStr"/>
       <c r="Z295" s="2" t="inlineStr"/>
+      <c r="AA295" s="2" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -24909,11 +25796,14 @@
       <c r="U296" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V296" s="2" t="inlineStr"/>
+      <c r="V296" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W296" s="2" t="inlineStr"/>
       <c r="X296" s="2" t="inlineStr"/>
       <c r="Y296" s="2" t="inlineStr"/>
       <c r="Z296" s="2" t="inlineStr"/>
+      <c r="AA296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -24983,11 +25873,14 @@
       <c r="U297" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V297" s="2" t="inlineStr"/>
+      <c r="V297" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W297" s="2" t="inlineStr"/>
       <c r="X297" s="2" t="inlineStr"/>
       <c r="Y297" s="2" t="inlineStr"/>
       <c r="Z297" s="2" t="inlineStr"/>
+      <c r="AA297" s="2" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -25057,15 +25950,18 @@
       <c r="U298" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V298" s="2" t="inlineStr">
+      <c r="V298" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W298" s="2" t="inlineStr">
         <is>
           <t>강냉이</t>
         </is>
       </c>
-      <c r="W298" s="2" t="inlineStr"/>
       <c r="X298" s="2" t="inlineStr"/>
       <c r="Y298" s="2" t="inlineStr"/>
       <c r="Z298" s="2" t="inlineStr"/>
+      <c r="AA298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -25155,15 +26051,18 @@
       <c r="U299" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V299" s="2" t="inlineStr">
+      <c r="V299" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W299" s="2" t="inlineStr">
         <is>
           <t>새우</t>
         </is>
       </c>
-      <c r="W299" s="2" t="inlineStr"/>
       <c r="X299" s="2" t="inlineStr"/>
       <c r="Y299" s="2" t="inlineStr"/>
       <c r="Z299" s="2" t="inlineStr"/>
+      <c r="AA299" s="2" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -25237,23 +26136,26 @@
       <c r="U300" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V300" s="2" t="inlineStr">
+      <c r="V300" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W300" s="2" t="inlineStr">
         <is>
           <t>빈대떡</t>
         </is>
       </c>
-      <c r="W300" s="2" t="inlineStr">
+      <c r="X300" s="2" t="inlineStr">
         <is>
           <t>송암동굴</t>
         </is>
       </c>
-      <c r="X300" s="2" t="inlineStr"/>
-      <c r="Y300" s="2" t="inlineStr">
+      <c r="Y300" s="2" t="inlineStr"/>
+      <c r="Z300" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z300" s="2" t="inlineStr"/>
+      <c r="AA300" s="2" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -25327,15 +26229,18 @@
       <c r="U301" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V301" s="2" t="inlineStr"/>
+      <c r="V301" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W301" s="2" t="inlineStr"/>
       <c r="X301" s="2" t="inlineStr"/>
-      <c r="Y301" s="2" t="inlineStr">
+      <c r="Y301" s="2" t="inlineStr"/>
+      <c r="Z301" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z301" s="2" t="inlineStr"/>
+      <c r="AA301" s="2" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -25409,15 +26314,18 @@
       <c r="U302" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V302" s="2" t="inlineStr">
+      <c r="V302" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W302" s="2" t="inlineStr">
         <is>
           <t>배추</t>
         </is>
       </c>
-      <c r="W302" s="2" t="inlineStr"/>
       <c r="X302" s="2" t="inlineStr"/>
       <c r="Y302" s="2" t="inlineStr"/>
       <c r="Z302" s="2" t="inlineStr"/>
+      <c r="AA302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -25499,23 +26407,26 @@
       <c r="U303" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V303" s="2" t="inlineStr">
+      <c r="V303" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W303" s="2" t="inlineStr">
         <is>
           <t>미나리</t>
         </is>
       </c>
-      <c r="W303" s="2" t="inlineStr">
+      <c r="X303" s="2" t="inlineStr">
         <is>
           <t>청천강 백사장</t>
         </is>
       </c>
-      <c r="X303" s="2" t="inlineStr"/>
-      <c r="Y303" s="2" t="inlineStr">
+      <c r="Y303" s="2" t="inlineStr"/>
+      <c r="Z303" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z303" s="2" t="inlineStr"/>
+      <c r="AA303" s="2" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -25589,15 +26500,18 @@
       <c r="U304" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V304" s="2" t="inlineStr"/>
+      <c r="V304" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W304" s="2" t="inlineStr"/>
       <c r="X304" s="2" t="inlineStr"/>
-      <c r="Y304" s="2" t="inlineStr">
+      <c r="Y304" s="2" t="inlineStr"/>
+      <c r="Z304" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z304" s="2" t="inlineStr"/>
+      <c r="AA304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -25671,15 +26585,18 @@
       <c r="U305" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V305" s="2" t="inlineStr"/>
+      <c r="V305" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W305" s="2" t="inlineStr"/>
       <c r="X305" s="2" t="inlineStr"/>
-      <c r="Y305" s="2" t="inlineStr">
+      <c r="Y305" s="2" t="inlineStr"/>
+      <c r="Z305" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z305" s="2" t="inlineStr"/>
+      <c r="AA305" s="2" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -25757,15 +26674,18 @@
       <c r="U306" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V306" s="2" t="inlineStr">
+      <c r="V306" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W306" s="2" t="inlineStr">
         <is>
           <t>맛조개</t>
         </is>
       </c>
-      <c r="W306" s="2" t="inlineStr"/>
       <c r="X306" s="2" t="inlineStr"/>
       <c r="Y306" s="2" t="inlineStr"/>
       <c r="Z306" s="2" t="inlineStr"/>
+      <c r="AA306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -25847,15 +26767,18 @@
       <c r="U307" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V307" s="2" t="inlineStr">
+      <c r="V307" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W307" s="2" t="inlineStr">
         <is>
           <t>백하젓</t>
         </is>
       </c>
-      <c r="W307" s="2" t="inlineStr"/>
       <c r="X307" s="2" t="inlineStr"/>
       <c r="Y307" s="2" t="inlineStr"/>
       <c r="Z307" s="2" t="inlineStr"/>
+      <c r="AA307" s="2" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -25929,15 +26852,18 @@
       <c r="U308" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V308" s="2" t="inlineStr">
+      <c r="V308" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W308" s="2" t="inlineStr">
         <is>
           <t>담배</t>
         </is>
       </c>
-      <c r="W308" s="2" t="inlineStr"/>
       <c r="X308" s="2" t="inlineStr"/>
       <c r="Y308" s="2" t="inlineStr"/>
       <c r="Z308" s="2" t="inlineStr"/>
+      <c r="AA308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -26019,15 +26945,18 @@
       <c r="U309" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V309" s="2" t="inlineStr"/>
+      <c r="V309" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W309" s="2" t="inlineStr"/>
       <c r="X309" s="2" t="inlineStr"/>
-      <c r="Y309" s="2" t="inlineStr">
+      <c r="Y309" s="2" t="inlineStr"/>
+      <c r="Z309" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z309" s="2" t="inlineStr"/>
+      <c r="AA309" s="2" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -26101,15 +27030,18 @@
       <c r="U310" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V310" s="2" t="inlineStr"/>
+      <c r="V310" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W310" s="2" t="inlineStr"/>
       <c r="X310" s="2" t="inlineStr"/>
-      <c r="Y310" s="2" t="inlineStr">
+      <c r="Y310" s="2" t="inlineStr"/>
+      <c r="Z310" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z310" s="2" t="inlineStr"/>
+      <c r="AA310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -26179,11 +27111,14 @@
       <c r="U311" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V311" s="2" t="inlineStr"/>
+      <c r="V311" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W311" s="2" t="inlineStr"/>
       <c r="X311" s="2" t="inlineStr"/>
       <c r="Y311" s="2" t="inlineStr"/>
       <c r="Z311" s="2" t="inlineStr"/>
+      <c r="AA311" s="2" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -26261,15 +27196,18 @@
       <c r="U312" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V312" s="2" t="inlineStr">
+      <c r="V312" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W312" s="2" t="inlineStr">
         <is>
           <t>증산 소금</t>
         </is>
       </c>
-      <c r="W312" s="2" t="inlineStr"/>
       <c r="X312" s="2" t="inlineStr"/>
       <c r="Y312" s="2" t="inlineStr"/>
       <c r="Z312" s="2" t="inlineStr"/>
+      <c r="AA312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -26339,11 +27277,14 @@
       <c r="U313" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V313" s="2" t="inlineStr"/>
+      <c r="V313" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W313" s="2" t="inlineStr"/>
       <c r="X313" s="2" t="inlineStr"/>
       <c r="Y313" s="2" t="inlineStr"/>
       <c r="Z313" s="2" t="inlineStr"/>
+      <c r="AA313" s="2" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -26413,15 +27354,18 @@
       <c r="U314" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V314" s="2" t="inlineStr"/>
+      <c r="V314" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W314" s="2" t="inlineStr"/>
       <c r="X314" s="2" t="inlineStr"/>
-      <c r="Y314" s="2" t="inlineStr">
+      <c r="Y314" s="2" t="inlineStr"/>
+      <c r="Z314" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z314" s="2" t="inlineStr"/>
+      <c r="AA314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -26491,15 +27435,18 @@
       <c r="U315" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V315" s="2" t="inlineStr">
+      <c r="V315" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W315" s="2" t="inlineStr">
         <is>
           <t>양덕 송이</t>
         </is>
       </c>
-      <c r="W315" s="2" t="inlineStr"/>
       <c r="X315" s="2" t="inlineStr"/>
       <c r="Y315" s="2" t="inlineStr"/>
       <c r="Z315" s="2" t="inlineStr"/>
+      <c r="AA315" s="2" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -26569,11 +27516,14 @@
       <c r="U316" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V316" s="2" t="inlineStr"/>
+      <c r="V316" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W316" s="2" t="inlineStr"/>
       <c r="X316" s="2" t="inlineStr"/>
       <c r="Y316" s="2" t="inlineStr"/>
       <c r="Z316" s="2" t="inlineStr"/>
+      <c r="AA316" s="2" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -26647,15 +27597,18 @@
       <c r="U317" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V317" s="2" t="inlineStr"/>
+      <c r="V317" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W317" s="2" t="inlineStr"/>
       <c r="X317" s="2" t="inlineStr"/>
-      <c r="Y317" s="2" t="inlineStr">
+      <c r="Y317" s="2" t="inlineStr"/>
+      <c r="Z317" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z317" s="2" t="inlineStr"/>
+      <c r="AA317" s="2" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -26729,19 +27682,22 @@
       <c r="U318" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V318" s="2" t="inlineStr">
+      <c r="V318" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W318" s="2" t="inlineStr">
         <is>
           <t>맹산 꿀</t>
         </is>
       </c>
-      <c r="W318" s="2" t="inlineStr"/>
       <c r="X318" s="2" t="inlineStr"/>
-      <c r="Y318" s="2" t="inlineStr">
+      <c r="Y318" s="2" t="inlineStr"/>
+      <c r="Z318" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z318" s="2" t="inlineStr"/>
+      <c r="AA318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -26815,11 +27771,14 @@
       <c r="U319" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V319" s="2" t="inlineStr"/>
+      <c r="V319" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W319" s="2" t="inlineStr"/>
       <c r="X319" s="2" t="inlineStr"/>
       <c r="Y319" s="2" t="inlineStr"/>
       <c r="Z319" s="2" t="inlineStr"/>
+      <c r="AA319" s="2" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -26893,15 +27852,18 @@
       <c r="U320" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V320" s="2" t="inlineStr">
+      <c r="V320" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W320" s="2" t="inlineStr">
         <is>
           <t>녕원 두릅</t>
         </is>
       </c>
-      <c r="W320" s="2" t="inlineStr"/>
       <c r="X320" s="2" t="inlineStr"/>
       <c r="Y320" s="2" t="inlineStr"/>
-      <c r="Z320" s="2" t="inlineStr">
+      <c r="Z320" s="2" t="inlineStr"/>
+      <c r="AA320" s="2" t="inlineStr">
         <is>
           <t>1 (수력(녕원))</t>
         </is>
@@ -26979,19 +27941,22 @@
       <c r="U321" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V321" s="2" t="inlineStr">
+      <c r="V321" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W321" s="2" t="inlineStr">
         <is>
           <t>고려인삼</t>
         </is>
       </c>
-      <c r="W321" s="2" t="inlineStr">
+      <c r="X321" s="2" t="inlineStr">
         <is>
           <t>박연폭포</t>
         </is>
       </c>
-      <c r="X321" s="2" t="inlineStr"/>
       <c r="Y321" s="2" t="inlineStr"/>
       <c r="Z321" s="2" t="inlineStr"/>
+      <c r="AA321" s="2" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -27073,11 +28038,14 @@
       <c r="U322" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V322" s="2" t="inlineStr"/>
+      <c r="V322" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W322" s="2" t="inlineStr"/>
       <c r="X322" s="2" t="inlineStr"/>
       <c r="Y322" s="2" t="inlineStr"/>
       <c r="Z322" s="2" t="inlineStr"/>
+      <c r="AA322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -27151,11 +28119,14 @@
       <c r="U323" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V323" s="2" t="inlineStr"/>
+      <c r="V323" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W323" s="2" t="inlineStr"/>
       <c r="X323" s="2" t="inlineStr"/>
       <c r="Y323" s="2" t="inlineStr"/>
       <c r="Z323" s="2" t="inlineStr"/>
+      <c r="AA323" s="2" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -27229,19 +28200,22 @@
       <c r="U324" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V324" s="2" t="inlineStr">
+      <c r="V324" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W324" s="2" t="inlineStr">
         <is>
           <t>사리원 포도</t>
         </is>
       </c>
-      <c r="W324" s="2" t="inlineStr"/>
       <c r="X324" s="2" t="inlineStr"/>
-      <c r="Y324" s="2" t="inlineStr">
+      <c r="Y324" s="2" t="inlineStr"/>
+      <c r="Z324" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z324" s="2" t="inlineStr"/>
+      <c r="AA324" s="2" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -27315,15 +28289,18 @@
       <c r="U325" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V325" s="2" t="inlineStr">
+      <c r="V325" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W325" s="2" t="inlineStr">
         <is>
           <t>황주 사과</t>
         </is>
       </c>
-      <c r="W325" s="2" t="inlineStr"/>
       <c r="X325" s="2" t="inlineStr"/>
       <c r="Y325" s="2" t="inlineStr"/>
       <c r="Z325" s="2" t="inlineStr"/>
+      <c r="AA325" s="2" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -27397,15 +28374,18 @@
       <c r="U326" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V326" s="2" t="inlineStr">
+      <c r="V326" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W326" s="2" t="inlineStr">
         <is>
           <t>자라</t>
         </is>
       </c>
-      <c r="W326" s="2" t="inlineStr"/>
       <c r="X326" s="2" t="inlineStr"/>
       <c r="Y326" s="2" t="inlineStr"/>
       <c r="Z326" s="2" t="inlineStr"/>
+      <c r="AA326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -27479,19 +28459,22 @@
       <c r="U327" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V327" s="2" t="inlineStr">
+      <c r="V327" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W327" s="2" t="inlineStr">
         <is>
           <t>백자</t>
         </is>
       </c>
-      <c r="W327" s="2" t="inlineStr"/>
       <c r="X327" s="2" t="inlineStr"/>
-      <c r="Y327" s="2" t="inlineStr">
+      <c r="Y327" s="2" t="inlineStr"/>
+      <c r="Z327" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z327" s="2" t="inlineStr"/>
+      <c r="AA327" s="2" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -27565,15 +28548,18 @@
       <c r="U328" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V328" s="2" t="inlineStr">
+      <c r="V328" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W328" s="2" t="inlineStr">
         <is>
           <t>평산 밤</t>
         </is>
       </c>
-      <c r="W328" s="2" t="inlineStr"/>
       <c r="X328" s="2" t="inlineStr"/>
       <c r="Y328" s="2" t="inlineStr"/>
       <c r="Z328" s="2" t="inlineStr"/>
+      <c r="AA328" s="2" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -27647,15 +28633,18 @@
       <c r="U329" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V329" s="2" t="inlineStr">
+      <c r="V329" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W329" s="2" t="inlineStr">
         <is>
           <t>꿀</t>
         </is>
       </c>
-      <c r="W329" s="2" t="inlineStr"/>
       <c r="X329" s="2" t="inlineStr"/>
       <c r="Y329" s="2" t="inlineStr"/>
       <c r="Z329" s="2" t="inlineStr"/>
+      <c r="AA329" s="2" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -27725,15 +28714,18 @@
       <c r="U330" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V330" s="2" t="inlineStr">
+      <c r="V330" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W330" s="2" t="inlineStr">
         <is>
           <t>대추</t>
         </is>
       </c>
-      <c r="W330" s="2" t="inlineStr"/>
       <c r="X330" s="2" t="inlineStr"/>
       <c r="Y330" s="2" t="inlineStr"/>
       <c r="Z330" s="2" t="inlineStr"/>
+      <c r="AA330" s="2" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -27807,15 +28799,18 @@
       <c r="U331" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V331" s="2" t="inlineStr">
+      <c r="V331" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W331" s="2" t="inlineStr">
         <is>
           <t>서흥 두릅</t>
         </is>
       </c>
-      <c r="W331" s="2" t="inlineStr"/>
       <c r="X331" s="2" t="inlineStr"/>
       <c r="Y331" s="2" t="inlineStr"/>
       <c r="Z331" s="2" t="inlineStr"/>
+      <c r="AA331" s="2" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -27885,11 +28880,14 @@
       <c r="U332" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V332" s="2" t="inlineStr"/>
+      <c r="V332" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W332" s="2" t="inlineStr"/>
       <c r="X332" s="2" t="inlineStr"/>
       <c r="Y332" s="2" t="inlineStr"/>
       <c r="Z332" s="2" t="inlineStr"/>
+      <c r="AA332" s="2" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -27959,11 +28957,14 @@
       <c r="U333" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V333" s="2" t="inlineStr"/>
+      <c r="V333" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W333" s="2" t="inlineStr"/>
       <c r="X333" s="2" t="inlineStr"/>
       <c r="Y333" s="2" t="inlineStr"/>
       <c r="Z333" s="2" t="inlineStr"/>
+      <c r="AA333" s="2" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -28037,15 +29038,18 @@
       <c r="U334" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V334" s="2" t="inlineStr">
+      <c r="V334" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W334" s="2" t="inlineStr">
         <is>
           <t>도라지</t>
         </is>
       </c>
-      <c r="W334" s="2" t="inlineStr"/>
       <c r="X334" s="2" t="inlineStr"/>
       <c r="Y334" s="2" t="inlineStr"/>
       <c r="Z334" s="2" t="inlineStr"/>
+      <c r="AA334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -28115,11 +29119,14 @@
       <c r="U335" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W335" s="2" t="inlineStr"/>
       <c r="X335" s="2" t="inlineStr"/>
       <c r="Y335" s="2" t="inlineStr"/>
       <c r="Z335" s="2" t="inlineStr"/>
+      <c r="AA335" s="2" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -28193,15 +29200,18 @@
       <c r="U336" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V336" s="2" t="inlineStr">
+      <c r="V336" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W336" s="2" t="inlineStr">
         <is>
           <t>금</t>
         </is>
       </c>
-      <c r="W336" s="2" t="inlineStr"/>
       <c r="X336" s="2" t="inlineStr"/>
       <c r="Y336" s="2" t="inlineStr"/>
       <c r="Z336" s="2" t="inlineStr"/>
+      <c r="AA336" s="2" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -28275,15 +29285,18 @@
       <c r="U337" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V337" s="2" t="inlineStr">
+      <c r="V337" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W337" s="2" t="inlineStr">
         <is>
           <t>잉어</t>
         </is>
       </c>
-      <c r="W337" s="2" t="inlineStr"/>
       <c r="X337" s="2" t="inlineStr"/>
       <c r="Y337" s="2" t="inlineStr"/>
       <c r="Z337" s="2" t="inlineStr"/>
+      <c r="AA337" s="2" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -28353,11 +29366,14 @@
       <c r="U338" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W338" s="2" t="inlineStr"/>
       <c r="X338" s="2" t="inlineStr"/>
       <c r="Y338" s="2" t="inlineStr"/>
       <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -28431,15 +29447,18 @@
       <c r="U339" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V339" s="2" t="inlineStr"/>
-      <c r="W339" s="2" t="inlineStr">
+      <c r="V339" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W339" s="2" t="inlineStr"/>
+      <c r="X339" s="2" t="inlineStr">
         <is>
           <t>송악산 만월대</t>
         </is>
       </c>
-      <c r="X339" s="2" t="inlineStr"/>
       <c r="Y339" s="2" t="inlineStr"/>
       <c r="Z339" s="2" t="inlineStr"/>
+      <c r="AA339" s="2" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -28513,11 +29532,14 @@
       <c r="U340" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V340" s="2" t="inlineStr"/>
+      <c r="V340" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W340" s="2" t="inlineStr"/>
       <c r="X340" s="2" t="inlineStr"/>
       <c r="Y340" s="2" t="inlineStr"/>
       <c r="Z340" s="2" t="inlineStr"/>
+      <c r="AA340" s="2" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -28591,11 +29613,14 @@
       <c r="U341" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V341" s="2" t="inlineStr"/>
+      <c r="V341" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W341" s="2" t="inlineStr"/>
       <c r="X341" s="2" t="inlineStr"/>
       <c r="Y341" s="2" t="inlineStr"/>
       <c r="Z341" s="2" t="inlineStr"/>
+      <c r="AA341" s="2" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -28665,15 +29690,18 @@
       <c r="U342" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V342" s="2" t="inlineStr"/>
-      <c r="W342" s="2" t="inlineStr">
+      <c r="V342" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W342" s="2" t="inlineStr"/>
+      <c r="X342" s="2" t="inlineStr">
         <is>
           <t>신평금강</t>
         </is>
       </c>
-      <c r="X342" s="2" t="inlineStr"/>
       <c r="Y342" s="2" t="inlineStr"/>
       <c r="Z342" s="2" t="inlineStr"/>
+      <c r="AA342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -28747,11 +29775,14 @@
       <c r="U343" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W343" s="2" t="inlineStr"/>
       <c r="X343" s="2" t="inlineStr"/>
       <c r="Y343" s="2" t="inlineStr"/>
       <c r="Z343" s="2" t="inlineStr"/>
+      <c r="AA343" s="2" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -28829,11 +29860,14 @@
       <c r="U344" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V344" s="2" t="n"/>
+      <c r="V344" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W344" s="2" t="n"/>
-      <c r="X344" s="2" t="inlineStr"/>
+      <c r="X344" s="2" t="n"/>
       <c r="Y344" s="2" t="inlineStr"/>
       <c r="Z344" s="2" t="inlineStr"/>
+      <c r="AA344" s="2" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -28909,17 +29943,20 @@
         <v>0</v>
       </c>
       <c r="U345" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V345" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V345" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W345" s="2" t="inlineStr">
         <is>
           <t>골뱅이</t>
         </is>
       </c>
-      <c r="W345" s="2" t="inlineStr"/>
       <c r="X345" s="2" t="inlineStr"/>
       <c r="Y345" s="2" t="inlineStr"/>
       <c r="Z345" s="2" t="inlineStr"/>
+      <c r="AA345" s="2" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -29001,15 +30038,18 @@
       <c r="U346" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V346" s="2" t="inlineStr">
+      <c r="V346" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W346" s="2" t="inlineStr">
         <is>
           <t>연백쌀</t>
         </is>
       </c>
-      <c r="W346" s="2" t="inlineStr"/>
       <c r="X346" s="2" t="inlineStr"/>
       <c r="Y346" s="2" t="inlineStr"/>
       <c r="Z346" s="2" t="inlineStr"/>
+      <c r="AA346" s="2" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -29087,15 +30127,18 @@
       <c r="U347" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V347" s="2" t="inlineStr">
+      <c r="V347" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W347" s="2" t="inlineStr">
         <is>
           <t>연안식해</t>
         </is>
       </c>
-      <c r="W347" s="2" t="inlineStr"/>
       <c r="X347" s="2" t="inlineStr"/>
       <c r="Y347" s="2" t="inlineStr"/>
       <c r="Z347" s="2" t="inlineStr"/>
+      <c r="AA347" s="2" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -29173,15 +30216,18 @@
       <c r="U348" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V348" s="2" t="inlineStr">
+      <c r="V348" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W348" s="2" t="inlineStr">
         <is>
           <t>청단 소금</t>
         </is>
       </c>
-      <c r="W348" s="2" t="inlineStr"/>
       <c r="X348" s="2" t="inlineStr"/>
       <c r="Y348" s="2" t="inlineStr"/>
       <c r="Z348" s="2" t="inlineStr"/>
+      <c r="AA348" s="2" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -29255,11 +30301,14 @@
       <c r="U349" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V349" s="2" t="inlineStr"/>
+      <c r="V349" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W349" s="2" t="inlineStr"/>
       <c r="X349" s="2" t="inlineStr"/>
       <c r="Y349" s="2" t="inlineStr"/>
       <c r="Z349" s="2" t="inlineStr"/>
+      <c r="AA349" s="2" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -29333,15 +30382,18 @@
       <c r="U350" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V350" s="2" t="inlineStr"/>
-      <c r="W350" s="2" t="inlineStr">
+      <c r="V350" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W350" s="2" t="inlineStr"/>
+      <c r="X350" s="2" t="inlineStr">
         <is>
           <t>구월산 사왕봉</t>
         </is>
       </c>
-      <c r="X350" s="2" t="inlineStr"/>
       <c r="Y350" s="2" t="inlineStr"/>
       <c r="Z350" s="2" t="inlineStr"/>
+      <c r="AA350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -29415,19 +30467,22 @@
       <c r="U351" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V351" s="2" t="inlineStr">
+      <c r="V351" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W351" s="2" t="inlineStr">
         <is>
           <t>재령 복숭아</t>
         </is>
       </c>
-      <c r="W351" s="2" t="inlineStr"/>
       <c r="X351" s="2" t="inlineStr"/>
-      <c r="Y351" s="2" t="inlineStr">
+      <c r="Y351" s="2" t="inlineStr"/>
+      <c r="Z351" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z351" s="2" t="inlineStr"/>
+      <c r="AA351" s="2" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -29505,15 +30560,18 @@
       <c r="U352" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V352" s="2" t="inlineStr">
+      <c r="V352" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W352" s="2" t="inlineStr">
         <is>
           <t>은률 밤</t>
         </is>
       </c>
-      <c r="W352" s="2" t="inlineStr"/>
       <c r="X352" s="2" t="inlineStr"/>
       <c r="Y352" s="2" t="inlineStr"/>
       <c r="Z352" s="2" t="inlineStr"/>
+      <c r="AA352" s="2" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -29591,15 +30649,18 @@
       <c r="U353" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V353" s="2" t="inlineStr">
+      <c r="V353" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W353" s="2" t="inlineStr">
         <is>
           <t>바지락</t>
         </is>
       </c>
-      <c r="W353" s="2" t="inlineStr"/>
       <c r="X353" s="2" t="inlineStr"/>
       <c r="Y353" s="2" t="inlineStr"/>
       <c r="Z353" s="2" t="inlineStr"/>
+      <c r="AA353" s="2" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -29673,11 +30734,14 @@
       <c r="U354" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V354" s="2" t="inlineStr"/>
+      <c r="V354" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W354" s="2" t="inlineStr"/>
       <c r="X354" s="2" t="inlineStr"/>
       <c r="Y354" s="2" t="inlineStr"/>
       <c r="Z354" s="2" t="inlineStr"/>
+      <c r="AA354" s="2" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -29759,19 +30823,22 @@
       <c r="U355" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V355" s="2" t="inlineStr">
+      <c r="V355" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W355" s="2" t="inlineStr">
         <is>
           <t>까나리</t>
         </is>
       </c>
-      <c r="W355" s="2" t="inlineStr">
+      <c r="X355" s="2" t="inlineStr">
         <is>
           <t>장산곶</t>
         </is>
       </c>
-      <c r="X355" s="2" t="inlineStr"/>
       <c r="Y355" s="2" t="inlineStr"/>
       <c r="Z355" s="2" t="inlineStr"/>
+      <c r="AA355" s="2" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -29849,15 +30916,18 @@
       <c r="U356" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V356" s="2" t="inlineStr"/>
-      <c r="W356" s="2" t="inlineStr">
+      <c r="V356" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W356" s="2" t="inlineStr"/>
+      <c r="X356" s="2" t="inlineStr">
         <is>
           <t>석담구곡</t>
         </is>
       </c>
-      <c r="X356" s="2" t="inlineStr"/>
       <c r="Y356" s="2" t="inlineStr"/>
       <c r="Z356" s="2" t="inlineStr"/>
+      <c r="AA356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -29939,19 +31009,22 @@
       <c r="U357" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V357" s="2" t="inlineStr">
+      <c r="V357" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W357" s="2" t="inlineStr">
         <is>
           <t>몽금포 전복</t>
         </is>
       </c>
-      <c r="W357" s="2" t="inlineStr">
+      <c r="X357" s="2" t="inlineStr">
         <is>
           <t>몽금포</t>
         </is>
       </c>
-      <c r="X357" s="2" t="inlineStr"/>
       <c r="Y357" s="2" t="inlineStr"/>
       <c r="Z357" s="2" t="inlineStr"/>
+      <c r="AA357" s="2" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -30029,15 +31102,18 @@
       <c r="U358" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V358" s="2" t="inlineStr">
+      <c r="V358" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W358" s="2" t="inlineStr">
         <is>
           <t>과일 사과</t>
         </is>
       </c>
-      <c r="W358" s="2" t="inlineStr"/>
       <c r="X358" s="2" t="inlineStr"/>
       <c r="Y358" s="2" t="inlineStr"/>
       <c r="Z358" s="2" t="inlineStr"/>
+      <c r="AA358" s="2" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -30111,11 +31187,14 @@
       <c r="U359" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V359" s="2" t="inlineStr"/>
+      <c r="V359" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W359" s="2" t="inlineStr"/>
       <c r="X359" s="2" t="inlineStr"/>
       <c r="Y359" s="2" t="inlineStr"/>
       <c r="Z359" s="2" t="inlineStr"/>
+      <c r="AA359" s="2" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -30185,15 +31264,18 @@
       <c r="U360" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V360" s="2" t="inlineStr"/>
-      <c r="W360" s="2" t="inlineStr">
+      <c r="V360" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W360" s="2" t="inlineStr"/>
+      <c r="X360" s="2" t="inlineStr">
         <is>
           <t>장수산 석동십이곡</t>
         </is>
       </c>
-      <c r="X360" s="2" t="inlineStr"/>
       <c r="Y360" s="2" t="inlineStr"/>
       <c r="Z360" s="2" t="inlineStr"/>
+      <c r="AA360" s="2" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -30267,11 +31349,14 @@
       <c r="U361" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V361" s="2" t="inlineStr"/>
+      <c r="V361" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W361" s="2" t="inlineStr"/>
       <c r="X361" s="2" t="inlineStr"/>
       <c r="Y361" s="2" t="inlineStr"/>
       <c r="Z361" s="2" t="inlineStr"/>
+      <c r="AA361" s="2" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -30353,11 +31438,14 @@
       <c r="U362" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V362" s="2" t="inlineStr"/>
+      <c r="V362" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W362" s="2" t="inlineStr"/>
       <c r="X362" s="2" t="inlineStr"/>
       <c r="Y362" s="2" t="inlineStr"/>
       <c r="Z362" s="2" t="inlineStr"/>
+      <c r="AA362" s="2" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -30435,11 +31523,14 @@
       <c r="U363" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V363" s="2" t="inlineStr"/>
+      <c r="V363" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W363" s="2" t="inlineStr"/>
       <c r="X363" s="2" t="inlineStr"/>
       <c r="Y363" s="2" t="inlineStr"/>
       <c r="Z363" s="2" t="inlineStr"/>
+      <c r="AA363" s="2" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -30515,17 +31606,20 @@
         <v>0</v>
       </c>
       <c r="U364" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V364" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V364" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W364" s="2" t="inlineStr">
         <is>
           <t>농마국수</t>
         </is>
       </c>
-      <c r="W364" s="2" t="inlineStr"/>
       <c r="X364" s="2" t="inlineStr"/>
       <c r="Y364" s="2" t="inlineStr"/>
       <c r="Z364" s="2" t="inlineStr"/>
+      <c r="AA364" s="2" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -30607,15 +31701,18 @@
       <c r="U365" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V365" s="2" t="inlineStr">
+      <c r="V365" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W365" s="2" t="inlineStr">
         <is>
           <t>백금</t>
         </is>
       </c>
-      <c r="W365" s="2" t="inlineStr"/>
       <c r="X365" s="2" t="inlineStr"/>
       <c r="Y365" s="2" t="inlineStr"/>
       <c r="Z365" s="2" t="inlineStr"/>
+      <c r="AA365" s="2" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -30697,11 +31794,14 @@
       <c r="U366" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V366" s="2" t="inlineStr"/>
+      <c r="V366" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W366" s="2" t="inlineStr"/>
       <c r="X366" s="2" t="inlineStr"/>
       <c r="Y366" s="2" t="inlineStr"/>
       <c r="Z366" s="2" t="inlineStr"/>
+      <c r="AA366" s="2" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -30783,15 +31883,18 @@
       <c r="U367" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V367" s="2" t="inlineStr">
+      <c r="V367" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W367" s="2" t="inlineStr">
         <is>
           <t>광포오리</t>
         </is>
       </c>
-      <c r="W367" s="2" t="inlineStr"/>
       <c r="X367" s="2" t="inlineStr"/>
       <c r="Y367" s="2" t="inlineStr"/>
       <c r="Z367" s="2" t="inlineStr"/>
+      <c r="AA367" s="2" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -30869,15 +31972,18 @@
       <c r="U368" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V368" s="2" t="inlineStr">
+      <c r="V368" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W368" s="2" t="inlineStr">
         <is>
           <t>물파</t>
         </is>
       </c>
-      <c r="W368" s="2" t="inlineStr"/>
       <c r="X368" s="2" t="inlineStr"/>
       <c r="Y368" s="2" t="inlineStr"/>
       <c r="Z368" s="2" t="inlineStr"/>
+      <c r="AA368" s="2" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -30955,15 +32061,18 @@
       <c r="U369" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V369" s="2" t="inlineStr">
+      <c r="V369" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W369" s="2" t="inlineStr">
         <is>
           <t>명란젓</t>
         </is>
       </c>
-      <c r="W369" s="2" t="inlineStr"/>
       <c r="X369" s="2" t="inlineStr"/>
       <c r="Y369" s="2" t="inlineStr"/>
       <c r="Z369" s="2" t="inlineStr"/>
+      <c r="AA369" s="2" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -31041,15 +32150,18 @@
       <c r="U370" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V370" s="2" t="inlineStr">
+      <c r="V370" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W370" s="2" t="inlineStr">
         <is>
           <t>홍원 털게</t>
         </is>
       </c>
-      <c r="W370" s="2" t="inlineStr"/>
       <c r="X370" s="2" t="inlineStr"/>
       <c r="Y370" s="2" t="inlineStr"/>
       <c r="Z370" s="2" t="inlineStr"/>
+      <c r="AA370" s="2" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -31127,11 +32239,14 @@
       <c r="U371" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V371" s="2" t="inlineStr"/>
+      <c r="V371" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W371" s="2" t="inlineStr"/>
       <c r="X371" s="2" t="inlineStr"/>
       <c r="Y371" s="2" t="inlineStr"/>
       <c r="Z371" s="2" t="inlineStr"/>
+      <c r="AA371" s="2" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -31209,15 +32324,18 @@
       <c r="U372" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V372" s="2" t="inlineStr">
+      <c r="V372" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W372" s="2" t="inlineStr">
         <is>
           <t>리원 오징어</t>
         </is>
       </c>
-      <c r="W372" s="2" t="inlineStr"/>
       <c r="X372" s="2" t="inlineStr"/>
       <c r="Y372" s="2" t="inlineStr"/>
       <c r="Z372" s="2" t="inlineStr"/>
+      <c r="AA372" s="2" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -31291,11 +32409,14 @@
       <c r="U373" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V373" s="2" t="inlineStr"/>
+      <c r="V373" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W373" s="2" t="inlineStr"/>
       <c r="X373" s="2" t="inlineStr"/>
       <c r="Y373" s="2" t="inlineStr"/>
-      <c r="Z373" s="2" t="inlineStr">
+      <c r="Z373" s="2" t="inlineStr"/>
+      <c r="AA373" s="2" t="inlineStr">
         <is>
           <t>1 (수력(허천강))</t>
         </is>
@@ -31373,11 +32494,14 @@
       <c r="U374" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V374" s="2" t="inlineStr"/>
+      <c r="V374" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W374" s="2" t="inlineStr"/>
       <c r="X374" s="2" t="inlineStr"/>
       <c r="Y374" s="2" t="inlineStr"/>
       <c r="Z374" s="2" t="inlineStr"/>
+      <c r="AA374" s="2" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -31447,11 +32571,14 @@
       <c r="U375" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V375" s="2" t="inlineStr"/>
+      <c r="V375" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W375" s="2" t="inlineStr"/>
       <c r="X375" s="2" t="inlineStr"/>
       <c r="Y375" s="2" t="inlineStr"/>
       <c r="Z375" s="2" t="inlineStr"/>
+      <c r="AA375" s="2" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -31521,11 +32648,14 @@
       <c r="U376" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V376" s="2" t="inlineStr"/>
+      <c r="V376" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W376" s="2" t="inlineStr"/>
       <c r="X376" s="2" t="inlineStr"/>
       <c r="Y376" s="2" t="inlineStr"/>
       <c r="Z376" s="2" t="inlineStr"/>
+      <c r="AA376" s="2" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -31599,15 +32729,18 @@
       <c r="U377" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V377" s="2" t="inlineStr"/>
+      <c r="V377" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W377" s="2" t="inlineStr"/>
       <c r="X377" s="2" t="inlineStr"/>
-      <c r="Y377" s="2" t="inlineStr">
+      <c r="Y377" s="2" t="inlineStr"/>
+      <c r="Z377" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z377" s="2" t="inlineStr"/>
+      <c r="AA377" s="2" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -31681,15 +32814,18 @@
       <c r="U378" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V378" s="2" t="inlineStr"/>
+      <c r="V378" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W378" s="2" t="inlineStr"/>
       <c r="X378" s="2" t="inlineStr"/>
-      <c r="Y378" s="2" t="inlineStr">
+      <c r="Y378" s="2" t="inlineStr"/>
+      <c r="Z378" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z378" s="2" t="inlineStr"/>
+      <c r="AA378" s="2" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -31763,19 +32899,22 @@
       <c r="U379" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V379" s="2" t="inlineStr">
+      <c r="V379" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W379" s="2" t="inlineStr">
         <is>
           <t>만삼</t>
         </is>
       </c>
-      <c r="W379" s="2" t="inlineStr">
+      <c r="X379" s="2" t="inlineStr">
         <is>
           <t>장진호</t>
         </is>
       </c>
-      <c r="X379" s="2" t="inlineStr"/>
       <c r="Y379" s="2" t="inlineStr"/>
-      <c r="Z379" s="2" t="inlineStr">
+      <c r="Z379" s="2" t="inlineStr"/>
+      <c r="AA379" s="2" t="inlineStr">
         <is>
           <t>1 (수력(장진강))</t>
         </is>
@@ -31849,11 +32988,14 @@
       <c r="U380" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V380" s="2" t="inlineStr"/>
+      <c r="V380" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W380" s="2" t="inlineStr"/>
       <c r="X380" s="2" t="inlineStr"/>
       <c r="Y380" s="2" t="inlineStr"/>
       <c r="Z380" s="2" t="inlineStr"/>
+      <c r="AA380" s="2" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -31927,19 +33069,22 @@
       <c r="U381" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V381" s="2" t="inlineStr">
+      <c r="V381" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W381" s="2" t="inlineStr">
         <is>
           <t>부전 감자</t>
         </is>
       </c>
-      <c r="W381" s="2" t="inlineStr">
+      <c r="X381" s="2" t="inlineStr">
         <is>
           <t>부전호</t>
         </is>
       </c>
-      <c r="X381" s="2" t="inlineStr"/>
       <c r="Y381" s="2" t="inlineStr"/>
-      <c r="Z381" s="2" t="inlineStr">
+      <c r="Z381" s="2" t="inlineStr"/>
+      <c r="AA381" s="2" t="inlineStr">
         <is>
           <t>1 (수력(부전강))</t>
         </is>
@@ -32017,11 +33162,14 @@
       <c r="U382" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V382" s="2" t="inlineStr"/>
+      <c r="V382" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W382" s="2" t="inlineStr"/>
       <c r="X382" s="2" t="inlineStr"/>
       <c r="Y382" s="2" t="inlineStr"/>
       <c r="Z382" s="2" t="inlineStr"/>
+      <c r="AA382" s="2" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -32091,11 +33239,14 @@
       <c r="U383" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V383" s="2" t="inlineStr"/>
+      <c r="V383" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W383" s="2" t="inlineStr"/>
       <c r="X383" s="2" t="inlineStr"/>
       <c r="Y383" s="2" t="inlineStr"/>
       <c r="Z383" s="2" t="inlineStr"/>
+      <c r="AA383" s="2" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -32175,17 +33326,20 @@
         <v>0</v>
       </c>
       <c r="U384" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V384" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V384" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W384" s="2" t="inlineStr">
         <is>
           <t>도루묵</t>
         </is>
       </c>
-      <c r="W384" s="2" t="inlineStr"/>
       <c r="X384" s="2" t="inlineStr"/>
       <c r="Y384" s="2" t="inlineStr"/>
       <c r="Z384" s="2" t="inlineStr"/>
+      <c r="AA384" s="2" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -32267,19 +33421,22 @@
       <c r="U385" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V385" s="2" t="inlineStr">
+      <c r="V385" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W385" s="2" t="inlineStr">
         <is>
           <t>성진 털게</t>
         </is>
       </c>
-      <c r="W385" s="2" t="inlineStr"/>
       <c r="X385" s="2" t="inlineStr"/>
-      <c r="Y385" s="2" t="inlineStr">
+      <c r="Y385" s="2" t="inlineStr"/>
+      <c r="Z385" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z385" s="2" t="inlineStr"/>
+      <c r="AA385" s="2" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -32349,19 +33506,22 @@
       <c r="U386" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V386" s="2" t="inlineStr">
+      <c r="V386" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W386" s="2" t="inlineStr">
         <is>
           <t>백살구</t>
         </is>
       </c>
-      <c r="W386" s="2" t="inlineStr"/>
       <c r="X386" s="2" t="inlineStr"/>
-      <c r="Y386" s="2" t="inlineStr">
+      <c r="Y386" s="2" t="inlineStr"/>
+      <c r="Z386" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z386" s="2" t="inlineStr"/>
+      <c r="AA386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -32435,19 +33595,22 @@
       <c r="U387" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V387" s="2" t="inlineStr">
+      <c r="V387" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W387" s="2" t="inlineStr">
         <is>
           <t>길주 모피</t>
         </is>
       </c>
-      <c r="W387" s="2" t="inlineStr"/>
       <c r="X387" s="2" t="inlineStr"/>
-      <c r="Y387" s="2" t="inlineStr">
+      <c r="Y387" s="2" t="inlineStr"/>
+      <c r="Z387" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z387" s="2" t="inlineStr"/>
+      <c r="AA387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -32517,19 +33680,22 @@
       <c r="U388" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V388" s="2" t="inlineStr">
+      <c r="V388" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W388" s="2" t="inlineStr">
         <is>
           <t>온성 모피</t>
         </is>
       </c>
-      <c r="W388" s="2" t="inlineStr"/>
       <c r="X388" s="2" t="inlineStr"/>
-      <c r="Y388" s="2" t="inlineStr">
+      <c r="Y388" s="2" t="inlineStr"/>
+      <c r="Z388" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z388" s="2" t="inlineStr"/>
+      <c r="AA388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -32603,15 +33769,18 @@
       <c r="U389" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V389" s="2" t="inlineStr">
+      <c r="V389" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W389" s="2" t="inlineStr">
         <is>
           <t>철광</t>
         </is>
       </c>
-      <c r="W389" s="2" t="inlineStr"/>
       <c r="X389" s="2" t="inlineStr"/>
       <c r="Y389" s="2" t="inlineStr"/>
       <c r="Z389" s="2" t="inlineStr"/>
+      <c r="AA389" s="2" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -32681,19 +33850,22 @@
       <c r="U390" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V390" s="2" t="inlineStr">
+      <c r="V390" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W390" s="2" t="inlineStr">
         <is>
           <t>경원 모피</t>
         </is>
       </c>
-      <c r="W390" s="2" t="inlineStr"/>
       <c r="X390" s="2" t="inlineStr"/>
-      <c r="Y390" s="2" t="inlineStr">
+      <c r="Y390" s="2" t="inlineStr"/>
+      <c r="Z390" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z390" s="2" t="inlineStr"/>
+      <c r="AA390" s="2" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -32775,19 +33947,22 @@
       <c r="U391" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V391" s="2" t="inlineStr">
+      <c r="V391" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W391" s="2" t="inlineStr">
         <is>
           <t>사기</t>
         </is>
       </c>
-      <c r="W391" s="2" t="inlineStr"/>
       <c r="X391" s="2" t="inlineStr"/>
-      <c r="Y391" s="2" t="inlineStr">
+      <c r="Y391" s="2" t="inlineStr"/>
+      <c r="Z391" s="2" t="inlineStr">
         <is>
           <t>②</t>
         </is>
       </c>
-      <c r="Z391" s="2" t="inlineStr"/>
+      <c r="AA391" s="2" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -32857,11 +34032,14 @@
       <c r="U392" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V392" s="2" t="inlineStr"/>
+      <c r="V392" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W392" s="2" t="inlineStr"/>
       <c r="X392" s="2" t="inlineStr"/>
       <c r="Y392" s="2" t="inlineStr"/>
       <c r="Z392" s="2" t="inlineStr"/>
+      <c r="AA392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -32931,15 +34109,18 @@
       <c r="U393" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V393" s="2" t="inlineStr"/>
+      <c r="V393" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W393" s="2" t="inlineStr"/>
       <c r="X393" s="2" t="inlineStr"/>
-      <c r="Y393" s="2" t="inlineStr">
+      <c r="Y393" s="2" t="inlineStr"/>
+      <c r="Z393" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z393" s="2" t="inlineStr"/>
+      <c r="AA393" s="2" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -33021,11 +34202,14 @@
       <c r="U394" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V394" s="2" t="inlineStr"/>
+      <c r="V394" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="W394" s="2" t="inlineStr"/>
       <c r="X394" s="2" t="inlineStr"/>
       <c r="Y394" s="2" t="inlineStr"/>
-      <c r="Z394" s="2" t="inlineStr">
+      <c r="Z394" s="2" t="inlineStr"/>
+      <c r="AA394" s="2" t="inlineStr">
         <is>
           <t>1 (수력(어랑천))</t>
         </is>
@@ -33107,23 +34291,26 @@
       <c r="U395" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V395" s="2" t="inlineStr">
+      <c r="V395" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W395" s="2" t="inlineStr">
         <is>
           <t>명태</t>
         </is>
       </c>
-      <c r="W395" s="2" t="inlineStr">
+      <c r="X395" s="2" t="inlineStr">
         <is>
           <t>무수단</t>
         </is>
       </c>
-      <c r="X395" s="2" t="inlineStr"/>
-      <c r="Y395" s="2" t="inlineStr">
+      <c r="Y395" s="2" t="inlineStr"/>
+      <c r="Z395" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z395" s="2" t="inlineStr"/>
+      <c r="AA395" s="2" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -33201,23 +34388,26 @@
       <c r="U396" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V396" s="2" t="inlineStr">
+      <c r="V396" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W396" s="2" t="inlineStr">
         <is>
           <t>약밤</t>
         </is>
       </c>
-      <c r="W396" s="2" t="inlineStr">
+      <c r="X396" s="2" t="inlineStr">
         <is>
           <t>칠보산 상매봉</t>
         </is>
       </c>
-      <c r="X396" s="2" t="inlineStr"/>
-      <c r="Y396" s="2" t="inlineStr">
+      <c r="Y396" s="2" t="inlineStr"/>
+      <c r="Z396" s="2" t="inlineStr">
         <is>
           <t>①</t>
         </is>
       </c>
-      <c r="Z396" s="2" t="inlineStr"/>
+      <c r="AA396" s="2" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -33291,11 +34481,14 @@
       <c r="U397" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V397" s="2" t="inlineStr"/>
+      <c r="V397" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W397" s="2" t="inlineStr"/>
       <c r="X397" s="2" t="inlineStr"/>
       <c r="Y397" s="2" t="inlineStr"/>
       <c r="Z397" s="2" t="inlineStr"/>
+      <c r="AA397" s="2" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -33369,11 +34562,14 @@
       <c r="U398" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V398" s="2" t="inlineStr"/>
+      <c r="V398" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W398" s="2" t="inlineStr"/>
       <c r="X398" s="2" t="inlineStr"/>
       <c r="Y398" s="2" t="inlineStr"/>
       <c r="Z398" s="2" t="inlineStr"/>
+      <c r="AA398" s="2" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -33443,15 +34639,18 @@
       <c r="U399" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V399" s="2" t="inlineStr">
+      <c r="V399" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W399" s="2" t="inlineStr">
         <is>
           <t>강계 모피</t>
         </is>
       </c>
-      <c r="W399" s="2" t="inlineStr"/>
       <c r="X399" s="2" t="inlineStr"/>
       <c r="Y399" s="2" t="inlineStr"/>
       <c r="Z399" s="2" t="inlineStr"/>
+      <c r="AA399" s="2" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -33525,15 +34724,18 @@
       <c r="U400" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V400" s="2" t="inlineStr">
+      <c r="V400" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W400" s="2" t="inlineStr">
         <is>
           <t>가죽</t>
         </is>
       </c>
-      <c r="W400" s="2" t="inlineStr"/>
       <c r="X400" s="2" t="inlineStr"/>
       <c r="Y400" s="2" t="inlineStr"/>
-      <c r="Z400" s="2" t="inlineStr">
+      <c r="Z400" s="2" t="inlineStr"/>
+      <c r="AA400" s="2" t="inlineStr">
         <is>
           <t>1 (수력(희천))</t>
         </is>
@@ -33607,11 +34809,14 @@
       <c r="U401" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V401" s="2" t="inlineStr"/>
+      <c r="V401" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W401" s="2" t="inlineStr"/>
       <c r="X401" s="2" t="inlineStr"/>
       <c r="Y401" s="2" t="inlineStr"/>
       <c r="Z401" s="2" t="inlineStr"/>
+      <c r="AA401" s="2" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -33685,11 +34890,14 @@
       <c r="U402" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V402" s="2" t="inlineStr"/>
+      <c r="V402" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W402" s="2" t="inlineStr"/>
       <c r="X402" s="2" t="inlineStr"/>
       <c r="Y402" s="2" t="inlineStr"/>
       <c r="Z402" s="2" t="inlineStr"/>
+      <c r="AA402" s="2" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -33763,11 +34971,14 @@
       <c r="U403" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V403" s="2" t="inlineStr"/>
+      <c r="V403" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W403" s="2" t="inlineStr"/>
       <c r="X403" s="2" t="inlineStr"/>
       <c r="Y403" s="2" t="inlineStr"/>
       <c r="Z403" s="2" t="inlineStr"/>
+      <c r="AA403" s="2" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -33837,15 +35048,18 @@
       <c r="U404" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V404" s="2" t="inlineStr">
+      <c r="V404" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W404" s="2" t="inlineStr">
         <is>
           <t>위원 잣</t>
         </is>
       </c>
-      <c r="W404" s="2" t="inlineStr"/>
       <c r="X404" s="2" t="inlineStr"/>
       <c r="Y404" s="2" t="inlineStr"/>
       <c r="Z404" s="2" t="inlineStr"/>
+      <c r="AA404" s="2" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -33919,11 +35133,14 @@
       <c r="U405" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V405" s="2" t="inlineStr"/>
+      <c r="V405" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W405" s="2" t="inlineStr"/>
       <c r="X405" s="2" t="inlineStr"/>
       <c r="Y405" s="2" t="inlineStr"/>
       <c r="Z405" s="2" t="inlineStr"/>
+      <c r="AA405" s="2" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -33993,11 +35210,14 @@
       <c r="U406" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V406" s="2" t="inlineStr"/>
+      <c r="V406" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W406" s="2" t="inlineStr"/>
       <c r="X406" s="2" t="inlineStr"/>
       <c r="Y406" s="2" t="inlineStr"/>
-      <c r="Z406" s="2" t="inlineStr">
+      <c r="Z406" s="2" t="inlineStr"/>
+      <c r="AA406" s="2" t="inlineStr">
         <is>
           <t>1 (수력(운봉))</t>
         </is>
@@ -34075,11 +35295,14 @@
       <c r="U407" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V407" s="2" t="inlineStr"/>
+      <c r="V407" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W407" s="2" t="inlineStr"/>
       <c r="X407" s="2" t="inlineStr"/>
       <c r="Y407" s="2" t="inlineStr"/>
       <c r="Z407" s="2" t="inlineStr"/>
+      <c r="AA407" s="2" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -34149,15 +35372,18 @@
       <c r="U408" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V408" s="2" t="inlineStr">
+      <c r="V408" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W408" s="2" t="inlineStr">
         <is>
           <t>창호지</t>
         </is>
       </c>
-      <c r="W408" s="2" t="inlineStr"/>
       <c r="X408" s="2" t="inlineStr"/>
       <c r="Y408" s="2" t="inlineStr"/>
       <c r="Z408" s="2" t="inlineStr"/>
+      <c r="AA408" s="2" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -34227,11 +35453,14 @@
       <c r="U409" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V409" s="2" t="inlineStr"/>
+      <c r="V409" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W409" s="2" t="inlineStr"/>
       <c r="X409" s="2" t="inlineStr"/>
       <c r="Y409" s="2" t="inlineStr"/>
       <c r="Z409" s="2" t="inlineStr"/>
+      <c r="AA409" s="2" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -34305,11 +35534,14 @@
       <c r="U410" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V410" s="2" t="inlineStr"/>
+      <c r="V410" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W410" s="2" t="inlineStr"/>
       <c r="X410" s="2" t="inlineStr"/>
       <c r="Y410" s="2" t="inlineStr"/>
       <c r="Z410" s="2" t="inlineStr"/>
+      <c r="AA410" s="2" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -34379,15 +35611,18 @@
       <c r="U411" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V411" s="2" t="inlineStr"/>
-      <c r="W411" s="2" t="inlineStr">
+      <c r="V411" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W411" s="2" t="inlineStr"/>
+      <c r="X411" s="2" t="inlineStr">
         <is>
           <t>시중호</t>
         </is>
       </c>
-      <c r="X411" s="2" t="inlineStr"/>
       <c r="Y411" s="2" t="inlineStr"/>
       <c r="Z411" s="2" t="inlineStr"/>
+      <c r="AA411" s="2" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -34457,11 +35692,14 @@
       <c r="U412" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V412" s="2" t="inlineStr"/>
+      <c r="V412" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W412" s="2" t="inlineStr"/>
       <c r="X412" s="2" t="inlineStr"/>
       <c r="Y412" s="2" t="inlineStr"/>
       <c r="Z412" s="2" t="inlineStr"/>
+      <c r="AA412" s="2" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -34535,11 +35773,14 @@
       <c r="U413" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V413" s="2" t="inlineStr"/>
+      <c r="V413" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W413" s="2" t="inlineStr"/>
       <c r="X413" s="2" t="inlineStr"/>
       <c r="Y413" s="2" t="inlineStr"/>
       <c r="Z413" s="2" t="inlineStr"/>
+      <c r="AA413" s="2" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -34613,15 +35854,18 @@
       <c r="U414" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V414" s="2" t="inlineStr">
+      <c r="V414" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W414" s="2" t="inlineStr">
         <is>
           <t>고사리</t>
         </is>
       </c>
-      <c r="W414" s="2" t="inlineStr"/>
       <c r="X414" s="2" t="inlineStr"/>
       <c r="Y414" s="2" t="inlineStr"/>
       <c r="Z414" s="2" t="inlineStr"/>
+      <c r="AA414" s="2" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -34695,15 +35939,18 @@
       <c r="U415" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V415" s="2" t="inlineStr">
+      <c r="V415" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W415" s="2" t="inlineStr">
         <is>
           <t>룡림 꿀</t>
         </is>
       </c>
-      <c r="W415" s="2" t="inlineStr"/>
       <c r="X415" s="2" t="inlineStr"/>
       <c r="Y415" s="2" t="inlineStr"/>
       <c r="Z415" s="2" t="inlineStr"/>
+      <c r="AA415" s="2" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -34773,11 +36020,14 @@
       <c r="U416" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V416" s="2" t="inlineStr"/>
+      <c r="V416" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W416" s="2" t="inlineStr"/>
       <c r="X416" s="2" t="inlineStr"/>
       <c r="Y416" s="2" t="inlineStr"/>
       <c r="Z416" s="2" t="inlineStr"/>
+      <c r="AA416" s="2" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -34847,15 +36097,18 @@
       <c r="U417" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V417" s="2" t="inlineStr">
+      <c r="V417" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W417" s="2" t="inlineStr">
         <is>
           <t>백두산 산삼</t>
         </is>
       </c>
-      <c r="W417" s="2" t="inlineStr"/>
       <c r="X417" s="2" t="inlineStr"/>
       <c r="Y417" s="2" t="inlineStr"/>
       <c r="Z417" s="2" t="inlineStr"/>
+      <c r="AA417" s="2" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -34929,15 +36182,18 @@
       <c r="U418" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V418" s="2" t="inlineStr">
+      <c r="V418" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W418" s="2" t="inlineStr">
         <is>
           <t>갑산 꿀</t>
         </is>
       </c>
-      <c r="W418" s="2" t="inlineStr"/>
       <c r="X418" s="2" t="inlineStr"/>
       <c r="Y418" s="2" t="inlineStr"/>
       <c r="Z418" s="2" t="inlineStr"/>
+      <c r="AA418" s="2" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -35011,15 +36267,18 @@
       <c r="U419" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V419" s="2" t="inlineStr">
+      <c r="V419" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W419" s="2" t="inlineStr">
         <is>
           <t>버섯</t>
         </is>
       </c>
-      <c r="W419" s="2" t="inlineStr"/>
       <c r="X419" s="2" t="inlineStr"/>
       <c r="Y419" s="2" t="inlineStr"/>
       <c r="Z419" s="2" t="inlineStr"/>
+      <c r="AA419" s="2" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -35093,11 +36352,14 @@
       <c r="U420" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V420" s="2" t="inlineStr"/>
+      <c r="V420" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W420" s="2" t="inlineStr"/>
       <c r="X420" s="2" t="inlineStr"/>
       <c r="Y420" s="2" t="inlineStr"/>
       <c r="Z420" s="2" t="inlineStr"/>
+      <c r="AA420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -35171,11 +36433,14 @@
       <c r="U421" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V421" s="2" t="inlineStr"/>
+      <c r="V421" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W421" s="2" t="inlineStr"/>
       <c r="X421" s="2" t="inlineStr"/>
       <c r="Y421" s="2" t="inlineStr"/>
       <c r="Z421" s="2" t="inlineStr"/>
+      <c r="AA421" s="2" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -35249,11 +36514,14 @@
       <c r="U422" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V422" s="2" t="inlineStr"/>
+      <c r="V422" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W422" s="2" t="inlineStr"/>
       <c r="X422" s="2" t="inlineStr"/>
       <c r="Y422" s="2" t="inlineStr"/>
       <c r="Z422" s="2" t="inlineStr"/>
+      <c r="AA422" s="2" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -35323,11 +36591,14 @@
       <c r="U423" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V423" s="2" t="inlineStr"/>
+      <c r="V423" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W423" s="2" t="inlineStr"/>
       <c r="X423" s="2" t="inlineStr"/>
       <c r="Y423" s="2" t="inlineStr"/>
       <c r="Z423" s="2" t="inlineStr"/>
+      <c r="AA423" s="2" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -35397,11 +36668,14 @@
       <c r="U424" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V424" s="2" t="inlineStr"/>
+      <c r="V424" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W424" s="2" t="inlineStr"/>
       <c r="X424" s="2" t="inlineStr"/>
       <c r="Y424" s="2" t="inlineStr"/>
       <c r="Z424" s="2" t="inlineStr"/>
+      <c r="AA424" s="2" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -35475,15 +36749,18 @@
       <c r="U425" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V425" s="2" t="inlineStr">
+      <c r="V425" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W425" s="2" t="inlineStr">
         <is>
           <t>풍산개</t>
         </is>
       </c>
-      <c r="W425" s="2" t="inlineStr"/>
       <c r="X425" s="2" t="inlineStr"/>
       <c r="Y425" s="2" t="inlineStr"/>
       <c r="Z425" s="2" t="inlineStr"/>
+      <c r="AA425" s="2" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -35553,11 +36830,14 @@
       <c r="U426" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V426" s="2" t="inlineStr"/>
+      <c r="V426" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W426" s="2" t="inlineStr"/>
       <c r="X426" s="2" t="inlineStr"/>
       <c r="Y426" s="2" t="inlineStr"/>
       <c r="Z426" s="2" t="inlineStr"/>
+      <c r="AA426" s="2" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -35631,15 +36911,18 @@
       <c r="U427" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V427" s="2" t="inlineStr">
+      <c r="V427" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W427" s="2" t="inlineStr">
         <is>
           <t>대홍단 감자</t>
         </is>
       </c>
-      <c r="W427" s="2" t="inlineStr"/>
       <c r="X427" s="2" t="inlineStr"/>
       <c r="Y427" s="2" t="inlineStr"/>
       <c r="Z427" s="2" t="inlineStr"/>
+      <c r="AA427" s="2" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -35713,19 +36996,22 @@
       <c r="U428" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="V428" s="2" t="inlineStr">
+      <c r="V428" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W428" s="2" t="inlineStr">
         <is>
           <t>들쭉</t>
         </is>
       </c>
-      <c r="W428" s="2" t="inlineStr">
+      <c r="X428" s="2" t="inlineStr">
         <is>
           <t>백두산 천지</t>
         </is>
       </c>
-      <c r="X428" s="2" t="inlineStr"/>
       <c r="Y428" s="2" t="inlineStr"/>
       <c r="Z428" s="2" t="inlineStr"/>
+      <c r="AA428" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
